--- a/panchang-data/Ayodhya2026.xlsx
+++ b/panchang-data/Ayodhya2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyotishiji.com\Base Files To Make New Panchang Excel Files\Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyotishiji.com\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E8CE93-AD17-4503-A391-973C376AF408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66E9186-C70B-4838-9236-3AE4B2C9AE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{8C4CE4A8-6776-4957-B4CF-7B8162B7DB7F}"/>
+    <workbookView xWindow="435" yWindow="2685" windowWidth="18570" windowHeight="11295" xr2:uid="{8C4CE4A8-6776-4957-B4CF-7B8162B7DB7F}"/>
   </bookViews>
   <sheets>
     <sheet name="WORD_954" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5400">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16225,17 +16225,19 @@
   </si>
   <si>
     <t>121°05'06.23</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="00"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16252,6 +16254,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Nirmala UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Nirmala UI"/>
       <family val="2"/>
@@ -16279,24 +16287,28 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16619,7 +16631,7 @@
     <col min="4" max="4" width="8.7109375" style="3" customWidth="1"/>
     <col min="5" max="19" width="16.7109375" style="4" customWidth="1"/>
     <col min="20" max="27" width="18.7109375" style="4" customWidth="1"/>
-    <col min="28" max="28" width="70.7109375" style="10" customWidth="1"/>
+    <col min="28" max="28" width="70.7109375" style="4" customWidth="1"/>
     <col min="29" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
@@ -16713,8 +16725,8 @@
       <c r="A2" s="1">
         <v>46023</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
+      <c r="B2" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16791,7 +16803,7 @@
       <c r="AA2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB2" s="9" t="s">
+      <c r="AB2" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -16799,8 +16811,8 @@
       <c r="A3" s="1">
         <v>46024</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
+      <c r="B3" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16877,7 +16889,7 @@
       <c r="AA3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -16885,8 +16897,8 @@
       <c r="A4" s="1">
         <v>46025</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
+      <c r="B4" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16963,7 +16975,7 @@
       <c r="AA4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -16971,8 +16983,8 @@
       <c r="A5" s="1">
         <v>46026</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
+      <c r="B5" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17049,7 +17061,7 @@
       <c r="AA5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AB5" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17057,8 +17069,8 @@
       <c r="A6" s="1">
         <v>46027</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
+      <c r="B6" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17135,7 +17147,7 @@
       <c r="AA6" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AB6" s="9" t="s">
+      <c r="AB6" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17143,8 +17155,8 @@
       <c r="A7" s="1">
         <v>46028</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>88</v>
+      <c r="B7" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17221,7 +17233,7 @@
       <c r="AA7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AB7" s="9" t="s">
+      <c r="AB7" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17229,8 +17241,8 @@
       <c r="A8" s="1">
         <v>46029</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>88</v>
+      <c r="B8" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17307,7 +17319,7 @@
       <c r="AA8" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="AB8" s="9" t="s">
+      <c r="AB8" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17315,8 +17327,8 @@
       <c r="A9" s="1">
         <v>46030</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>88</v>
+      <c r="B9" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17393,7 +17405,7 @@
       <c r="AA9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AB9" s="9" t="s">
+      <c r="AB9" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17401,8 +17413,8 @@
       <c r="A10" s="1">
         <v>46031</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>88</v>
+      <c r="B10" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17479,7 +17491,7 @@
       <c r="AA10" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AB10" s="9" t="s">
+      <c r="AB10" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17487,8 +17499,8 @@
       <c r="A11" s="1">
         <v>46032</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17565,7 +17577,7 @@
       <c r="AA11" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AB11" s="9" t="s">
+      <c r="AB11" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17573,8 +17585,8 @@
       <c r="A12" s="1">
         <v>46033</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>88</v>
+      <c r="B12" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17651,7 +17663,7 @@
       <c r="AA12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AB12" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17659,8 +17671,8 @@
       <c r="A13" s="1">
         <v>46034</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>88</v>
+      <c r="B13" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17737,7 +17749,7 @@
       <c r="AA13" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="AB13" s="9" t="s">
+      <c r="AB13" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17745,8 +17757,8 @@
       <c r="A14" s="1">
         <v>46035</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>88</v>
+      <c r="B14" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17823,7 +17835,7 @@
       <c r="AA14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AB14" s="9" t="s">
+      <c r="AB14" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17831,8 +17843,8 @@
       <c r="A15" s="1">
         <v>46036</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>88</v>
+      <c r="B15" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17909,7 +17921,7 @@
       <c r="AA15" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AB15" s="9" t="s">
+      <c r="AB15" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -17917,8 +17929,8 @@
       <c r="A16" s="1">
         <v>46037</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>88</v>
+      <c r="B16" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17995,7 +18007,7 @@
       <c r="AA16" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AB16" s="9" t="s">
+      <c r="AB16" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18003,8 +18015,8 @@
       <c r="A17" s="1">
         <v>46038</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>88</v>
+      <c r="B17" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18081,7 +18093,7 @@
       <c r="AA17" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AB17" s="9" t="s">
+      <c r="AB17" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18089,8 +18101,8 @@
       <c r="A18" s="1">
         <v>46039</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>88</v>
+      <c r="B18" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18167,7 +18179,7 @@
       <c r="AA18" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AB18" s="9" t="s">
+      <c r="AB18" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18175,8 +18187,8 @@
       <c r="A19" s="1">
         <v>46040</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>88</v>
+      <c r="B19" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18253,7 +18265,7 @@
       <c r="AA19" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="AB19" s="9" t="s">
+      <c r="AB19" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18261,8 +18273,8 @@
       <c r="A20" s="1">
         <v>46041</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>88</v>
+      <c r="B20" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18339,7 +18351,7 @@
       <c r="AA20" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="AB20" s="9" t="s">
+      <c r="AB20" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18347,8 +18359,8 @@
       <c r="A21" s="1">
         <v>46042</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>88</v>
+      <c r="B21" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18425,7 +18437,7 @@
       <c r="AA21" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="AB21" s="9" t="s">
+      <c r="AB21" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18433,8 +18445,8 @@
       <c r="A22" s="1">
         <v>46043</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>88</v>
+      <c r="B22" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18511,7 +18523,7 @@
       <c r="AA22" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="AB22" s="9" t="s">
+      <c r="AB22" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18519,8 +18531,8 @@
       <c r="A23" s="1">
         <v>46044</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>88</v>
+      <c r="B23" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18597,7 +18609,7 @@
       <c r="AA23" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="AB23" s="9" t="s">
+      <c r="AB23" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18605,8 +18617,8 @@
       <c r="A24" s="1">
         <v>46045</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
+      <c r="B24" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18683,7 +18695,7 @@
       <c r="AA24" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="AB24" s="9" t="s">
+      <c r="AB24" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18691,8 +18703,8 @@
       <c r="A25" s="1">
         <v>46046</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>88</v>
+      <c r="B25" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18769,7 +18781,7 @@
       <c r="AA25" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="AB25" s="9" t="s">
+      <c r="AB25" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18777,8 +18789,8 @@
       <c r="A26" s="1">
         <v>46047</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>88</v>
+      <c r="B26" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18855,7 +18867,7 @@
       <c r="AA26" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="AB26" s="9" t="s">
+      <c r="AB26" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18863,8 +18875,8 @@
       <c r="A27" s="1">
         <v>46048</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
+      <c r="B27" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18941,7 +18953,7 @@
       <c r="AA27" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="AB27" s="9" t="s">
+      <c r="AB27" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -18949,8 +18961,8 @@
       <c r="A28" s="1">
         <v>46049</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>88</v>
+      <c r="B28" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19027,7 +19039,7 @@
       <c r="AA28" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AB28" s="9" t="s">
+      <c r="AB28" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19035,8 +19047,8 @@
       <c r="A29" s="1">
         <v>46050</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>88</v>
+      <c r="B29" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19113,7 +19125,7 @@
       <c r="AA29" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="AB29" s="9" t="s">
+      <c r="AB29" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19121,8 +19133,8 @@
       <c r="A30" s="1">
         <v>46051</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>88</v>
+      <c r="B30" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19199,7 +19211,7 @@
       <c r="AA30" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AB30" s="9" t="s">
+      <c r="AB30" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19207,8 +19219,8 @@
       <c r="A31" s="1">
         <v>46052</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>88</v>
+      <c r="B31" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19285,7 +19297,7 @@
       <c r="AA31" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="AB31" s="9" t="s">
+      <c r="AB31" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19293,8 +19305,8 @@
       <c r="A32" s="1">
         <v>46053</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>88</v>
+      <c r="B32" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19371,7 +19383,7 @@
       <c r="AA32" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="AB32" s="9" t="s">
+      <c r="AB32" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19379,8 +19391,8 @@
       <c r="A33" s="1">
         <v>46054</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>88</v>
+      <c r="B33" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19457,7 +19469,7 @@
       <c r="AA33" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="AB33" s="9" t="s">
+      <c r="AB33" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19465,8 +19477,8 @@
       <c r="A34" s="1">
         <v>46055</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>561</v>
+      <c r="B34" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19543,7 +19555,7 @@
       <c r="AA34" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="AB34" s="9" t="s">
+      <c r="AB34" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19551,8 +19563,8 @@
       <c r="A35" s="1">
         <v>46056</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>561</v>
+      <c r="B35" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19629,7 +19641,7 @@
       <c r="AA35" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="AB35" s="9" t="s">
+      <c r="AB35" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19637,8 +19649,8 @@
       <c r="A36" s="1">
         <v>46057</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>561</v>
+      <c r="B36" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19715,7 +19727,7 @@
       <c r="AA36" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="AB36" s="9" t="s">
+      <c r="AB36" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19723,8 +19735,8 @@
       <c r="A37" s="1">
         <v>46058</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>561</v>
+      <c r="B37" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19801,7 +19813,7 @@
       <c r="AA37" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="AB37" s="9" t="s">
+      <c r="AB37" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19809,8 +19821,8 @@
       <c r="A38" s="1">
         <v>46059</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>561</v>
+      <c r="B38" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19887,7 +19899,7 @@
       <c r="AA38" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="AB38" s="9" t="s">
+      <c r="AB38" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19895,8 +19907,8 @@
       <c r="A39" s="1">
         <v>46060</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>561</v>
+      <c r="B39" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19973,7 +19985,7 @@
       <c r="AA39" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="AB39" s="9" t="s">
+      <c r="AB39" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -19981,8 +19993,8 @@
       <c r="A40" s="1">
         <v>46061</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>561</v>
+      <c r="B40" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20059,7 +20071,7 @@
       <c r="AA40" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="AB40" s="9" t="s">
+      <c r="AB40" s="2" t="s">
         <v>467</v>
       </c>
     </row>
@@ -20067,8 +20079,8 @@
       <c r="A41" s="1">
         <v>46062</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>561</v>
+      <c r="B41" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20145,7 +20157,7 @@
       <c r="AA41" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="AB41" s="9" t="s">
+      <c r="AB41" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20153,8 +20165,8 @@
       <c r="A42" s="1">
         <v>46063</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>561</v>
+      <c r="B42" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20231,7 +20243,7 @@
       <c r="AA42" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="AB42" s="9" t="s">
+      <c r="AB42" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20239,8 +20251,8 @@
       <c r="A43" s="1">
         <v>46064</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>561</v>
+      <c r="B43" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20317,7 +20329,7 @@
       <c r="AA43" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="AB43" s="9" t="s">
+      <c r="AB43" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20325,8 +20337,8 @@
       <c r="A44" s="1">
         <v>46065</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>561</v>
+      <c r="B44" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20403,7 +20415,7 @@
       <c r="AA44" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="AB44" s="9" t="s">
+      <c r="AB44" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20411,8 +20423,8 @@
       <c r="A45" s="1">
         <v>46066</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>561</v>
+      <c r="B45" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20489,7 +20501,7 @@
       <c r="AA45" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="AB45" s="9" t="s">
+      <c r="AB45" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20497,8 +20509,8 @@
       <c r="A46" s="1">
         <v>46067</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>561</v>
+      <c r="B46" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20575,7 +20587,7 @@
       <c r="AA46" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="AB46" s="9" t="s">
+      <c r="AB46" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20583,8 +20595,8 @@
       <c r="A47" s="1">
         <v>46068</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>561</v>
+      <c r="B47" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20661,7 +20673,7 @@
       <c r="AA47" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="AB47" s="9" t="s">
+      <c r="AB47" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20669,8 +20681,8 @@
       <c r="A48" s="1">
         <v>46069</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>561</v>
+      <c r="B48" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20747,7 +20759,7 @@
       <c r="AA48" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="AB48" s="9" t="s">
+      <c r="AB48" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20755,8 +20767,8 @@
       <c r="A49" s="1">
         <v>46070</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>561</v>
+      <c r="B49" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20833,7 +20845,7 @@
       <c r="AA49" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="AB49" s="9" t="s">
+      <c r="AB49" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20841,8 +20853,8 @@
       <c r="A50" s="1">
         <v>46071</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>561</v>
+      <c r="B50" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20919,7 +20931,7 @@
       <c r="AA50" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="AB50" s="9" t="s">
+      <c r="AB50" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -20927,8 +20939,8 @@
       <c r="A51" s="1">
         <v>46072</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>561</v>
+      <c r="B51" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21005,7 +21017,7 @@
       <c r="AA51" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="AB51" s="9" t="s">
+      <c r="AB51" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21013,8 +21025,8 @@
       <c r="A52" s="1">
         <v>46073</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>561</v>
+      <c r="B52" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21091,7 +21103,7 @@
       <c r="AA52" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="AB52" s="9" t="s">
+      <c r="AB52" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21099,8 +21111,8 @@
       <c r="A53" s="1">
         <v>46074</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>561</v>
+      <c r="B53" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21177,7 +21189,7 @@
       <c r="AA53" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="AB53" s="9" t="s">
+      <c r="AB53" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21185,8 +21197,8 @@
       <c r="A54" s="1">
         <v>46075</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>561</v>
+      <c r="B54" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21263,7 +21275,7 @@
       <c r="AA54" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="AB54" s="9" t="s">
+      <c r="AB54" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21271,8 +21283,8 @@
       <c r="A55" s="1">
         <v>46076</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>561</v>
+      <c r="B55" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21349,7 +21361,7 @@
       <c r="AA55" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="AB55" s="9" t="s">
+      <c r="AB55" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21357,8 +21369,8 @@
       <c r="A56" s="1">
         <v>46077</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>561</v>
+      <c r="B56" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21435,7 +21447,7 @@
       <c r="AA56" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="AB56" s="9" t="s">
+      <c r="AB56" s="2" t="s">
         <v>679</v>
       </c>
     </row>
@@ -21443,8 +21455,8 @@
       <c r="A57" s="1">
         <v>46078</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>561</v>
+      <c r="B57" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21521,7 +21533,7 @@
       <c r="AA57" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="AB57" s="9" t="s">
+      <c r="AB57" s="2" t="s">
         <v>913</v>
       </c>
     </row>
@@ -21529,8 +21541,8 @@
       <c r="A58" s="1">
         <v>46079</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>561</v>
+      <c r="B58" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21607,7 +21619,7 @@
       <c r="AA58" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="AB58" s="9" t="s">
+      <c r="AB58" s="2" t="s">
         <v>913</v>
       </c>
     </row>
@@ -21615,8 +21627,8 @@
       <c r="A59" s="1">
         <v>46080</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>561</v>
+      <c r="B59" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21693,7 +21705,7 @@
       <c r="AA59" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="AB59" s="9" t="s">
+      <c r="AB59" s="2" t="s">
         <v>913</v>
       </c>
     </row>
@@ -21701,8 +21713,8 @@
       <c r="A60" s="1">
         <v>46081</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>561</v>
+      <c r="B60" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21779,7 +21791,7 @@
       <c r="AA60" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="AB60" s="9" t="s">
+      <c r="AB60" s="2" t="s">
         <v>957</v>
       </c>
     </row>
@@ -21787,8 +21799,8 @@
       <c r="A61" s="1">
         <v>46082</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>561</v>
+      <c r="B61" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21865,7 +21877,7 @@
       <c r="AA61" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="AB61" s="9" t="s">
+      <c r="AB61" s="2" t="s">
         <v>973</v>
       </c>
     </row>
@@ -21873,8 +21885,8 @@
       <c r="A62" s="1">
         <v>46083</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>561</v>
+      <c r="B62" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21951,7 +21963,7 @@
       <c r="AA62" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="AB62" s="9" t="s">
+      <c r="AB62" s="2" t="s">
         <v>973</v>
       </c>
     </row>
@@ -21959,8 +21971,8 @@
       <c r="A63" s="1">
         <v>46084</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>561</v>
+      <c r="B63" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22037,7 +22049,7 @@
       <c r="AA63" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="AB63" s="9" t="s">
+      <c r="AB63" s="2" t="s">
         <v>973</v>
       </c>
     </row>
@@ -22045,8 +22057,8 @@
       <c r="A64" s="1">
         <v>46085</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>1002</v>
+      <c r="B64" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22123,7 +22135,7 @@
       <c r="AA64" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="AB64" s="9" t="s">
+      <c r="AB64" s="2" t="s">
         <v>973</v>
       </c>
     </row>
@@ -22131,8 +22143,8 @@
       <c r="A65" s="1">
         <v>46086</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>1002</v>
+      <c r="B65" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22209,7 +22221,7 @@
       <c r="AA65" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="AB65" s="9" t="s">
+      <c r="AB65" s="2" t="s">
         <v>973</v>
       </c>
     </row>
@@ -22217,8 +22229,8 @@
       <c r="A66" s="1">
         <v>46087</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>1002</v>
+      <c r="B66" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22295,7 +22307,7 @@
       <c r="AA66" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="AB66" s="9" t="s">
+      <c r="AB66" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22303,8 +22315,8 @@
       <c r="A67" s="1">
         <v>46088</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>1002</v>
+      <c r="B67" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22381,7 +22393,7 @@
       <c r="AA67" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="AB67" s="9" t="s">
+      <c r="AB67" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22389,8 +22401,8 @@
       <c r="A68" s="1">
         <v>46089</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>1002</v>
+      <c r="B68" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22467,7 +22479,7 @@
       <c r="AA68" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="AB68" s="9" t="s">
+      <c r="AB68" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22475,8 +22487,8 @@
       <c r="A69" s="1">
         <v>46090</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>1002</v>
+      <c r="B69" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22553,7 +22565,7 @@
       <c r="AA69" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="AB69" s="9" t="s">
+      <c r="AB69" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22561,8 +22573,8 @@
       <c r="A70" s="1">
         <v>46091</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>1002</v>
+      <c r="B70" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22639,7 +22651,7 @@
       <c r="AA70" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="AB70" s="9" t="s">
+      <c r="AB70" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22647,8 +22659,8 @@
       <c r="A71" s="1">
         <v>46092</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>1002</v>
+      <c r="B71" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22725,7 +22737,7 @@
       <c r="AA71" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="AB71" s="9" t="s">
+      <c r="AB71" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22733,8 +22745,8 @@
       <c r="A72" s="1">
         <v>46093</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>1002</v>
+      <c r="B72" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22811,7 +22823,7 @@
       <c r="AA72" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="AB72" s="9" t="s">
+      <c r="AB72" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22819,8 +22831,8 @@
       <c r="A73" s="1">
         <v>46094</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>1002</v>
+      <c r="B73" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22897,7 +22909,7 @@
       <c r="AA73" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="AB73" s="9" t="s">
+      <c r="AB73" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22905,8 +22917,8 @@
       <c r="A74" s="1">
         <v>46095</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>1002</v>
+      <c r="B74" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22983,7 +22995,7 @@
       <c r="AA74" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="AB74" s="9" t="s">
+      <c r="AB74" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -22991,8 +23003,8 @@
       <c r="A75" s="1">
         <v>46096</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>1002</v>
+      <c r="B75" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23069,7 +23081,7 @@
       <c r="AA75" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="AB75" s="9" t="s">
+      <c r="AB75" s="2" t="s">
         <v>1176</v>
       </c>
     </row>
@@ -23077,8 +23089,8 @@
       <c r="A76" s="1">
         <v>46097</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>1002</v>
+      <c r="B76" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23155,7 +23167,7 @@
       <c r="AA76" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="AB76" s="9" t="s">
+      <c r="AB76" s="2" t="s">
         <v>1176</v>
       </c>
     </row>
@@ -23163,8 +23175,8 @@
       <c r="A77" s="1">
         <v>46098</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>1002</v>
+      <c r="B77" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23241,7 +23253,7 @@
       <c r="AA77" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="AB77" s="9" t="s">
+      <c r="AB77" s="2" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -23249,8 +23261,8 @@
       <c r="A78" s="1">
         <v>46099</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>1002</v>
+      <c r="B78" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23327,7 +23339,7 @@
       <c r="AA78" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="AB78" s="9" t="s">
+      <c r="AB78" s="2" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -23335,8 +23347,8 @@
       <c r="A79" s="1">
         <v>46100</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>1002</v>
+      <c r="B79" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23413,7 +23425,7 @@
       <c r="AA79" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="AB79" s="9" t="s">
+      <c r="AB79" s="2" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -23421,8 +23433,8 @@
       <c r="A80" s="1">
         <v>46101</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>1002</v>
+      <c r="B80" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23499,7 +23511,7 @@
       <c r="AA80" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="AB80" s="9" t="s">
+      <c r="AB80" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23507,8 +23519,8 @@
       <c r="A81" s="1">
         <v>46102</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>1002</v>
+      <c r="B81" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23585,7 +23597,7 @@
       <c r="AA81" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="AB81" s="9" t="s">
+      <c r="AB81" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23593,8 +23605,8 @@
       <c r="A82" s="1">
         <v>46103</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>1002</v>
+      <c r="B82" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23671,7 +23683,7 @@
       <c r="AA82" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="AB82" s="9" t="s">
+      <c r="AB82" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23679,8 +23691,8 @@
       <c r="A83" s="1">
         <v>46104</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>1002</v>
+      <c r="B83" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23757,7 +23769,7 @@
       <c r="AA83" s="2" t="s">
         <v>1296</v>
       </c>
-      <c r="AB83" s="9" t="s">
+      <c r="AB83" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23765,8 +23777,8 @@
       <c r="A84" s="1">
         <v>46105</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>1002</v>
+      <c r="B84" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23843,7 +23855,7 @@
       <c r="AA84" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="AB84" s="9" t="s">
+      <c r="AB84" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23851,8 +23863,8 @@
       <c r="A85" s="1">
         <v>46106</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>1002</v>
+      <c r="B85" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23929,7 +23941,7 @@
       <c r="AA85" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="AB85" s="9" t="s">
+      <c r="AB85" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -23937,8 +23949,8 @@
       <c r="A86" s="1">
         <v>46107</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>1002</v>
+      <c r="B86" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24015,7 +24027,7 @@
       <c r="AA86" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="AB86" s="9" t="s">
+      <c r="AB86" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24023,8 +24035,8 @@
       <c r="A87" s="1">
         <v>46108</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>1002</v>
+      <c r="B87" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24101,7 +24113,7 @@
       <c r="AA87" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="AB87" s="9" t="s">
+      <c r="AB87" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24109,8 +24121,8 @@
       <c r="A88" s="1">
         <v>46109</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>1002</v>
+      <c r="B88" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24187,7 +24199,7 @@
       <c r="AA88" s="2" t="s">
         <v>1370</v>
       </c>
-      <c r="AB88" s="9" t="s">
+      <c r="AB88" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24195,8 +24207,8 @@
       <c r="A89" s="1">
         <v>46110</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>1002</v>
+      <c r="B89" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24273,7 +24285,7 @@
       <c r="AA89" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="AB89" s="9" t="s">
+      <c r="AB89" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24281,8 +24293,8 @@
       <c r="A90" s="1">
         <v>46111</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>1002</v>
+      <c r="B90" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24359,7 +24371,7 @@
       <c r="AA90" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="AB90" s="9" t="s">
+      <c r="AB90" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24367,8 +24379,8 @@
       <c r="A91" s="1">
         <v>46112</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>1002</v>
+      <c r="B91" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24445,7 +24457,7 @@
       <c r="AA91" s="2" t="s">
         <v>1413</v>
       </c>
-      <c r="AB91" s="9" t="s">
+      <c r="AB91" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24453,8 +24465,8 @@
       <c r="A92" s="1">
         <v>46113</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>1002</v>
+      <c r="B92" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24531,7 +24543,7 @@
       <c r="AA92" s="2" t="s">
         <v>1427</v>
       </c>
-      <c r="AB92" s="9" t="s">
+      <c r="AB92" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24539,8 +24551,8 @@
       <c r="A93" s="1">
         <v>46114</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>1002</v>
+      <c r="B93" s="9" t="s">
+        <v>1443</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24617,7 +24629,7 @@
       <c r="AA93" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="AB93" s="9" t="s">
+      <c r="AB93" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -24625,8 +24637,8 @@
       <c r="A94" s="1">
         <v>46115</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>1443</v>
+      <c r="B94" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24703,7 +24715,7 @@
       <c r="AA94" s="2" t="s">
         <v>1457</v>
       </c>
-      <c r="AB94" s="9" t="s">
+      <c r="AB94" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -24711,8 +24723,8 @@
       <c r="A95" s="1">
         <v>46116</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>1443</v>
+      <c r="B95" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24789,7 +24801,7 @@
       <c r="AA95" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="AB95" s="9" t="s">
+      <c r="AB95" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -24797,8 +24809,8 @@
       <c r="A96" s="1">
         <v>46117</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>1443</v>
+      <c r="B96" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24875,7 +24887,7 @@
       <c r="AA96" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="AB96" s="9" t="s">
+      <c r="AB96" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -24883,8 +24895,8 @@
       <c r="A97" s="1">
         <v>46118</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>1443</v>
+      <c r="B97" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24961,7 +24973,7 @@
       <c r="AA97" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="AB97" s="9" t="s">
+      <c r="AB97" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -24969,8 +24981,8 @@
       <c r="A98" s="1">
         <v>46119</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>1443</v>
+      <c r="B98" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25047,7 +25059,7 @@
       <c r="AA98" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="AB98" s="9" t="s">
+      <c r="AB98" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -25055,8 +25067,8 @@
       <c r="A99" s="1">
         <v>46120</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>1443</v>
+      <c r="B99" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25133,7 +25145,7 @@
       <c r="AA99" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="AB99" s="9" t="s">
+      <c r="AB99" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -25141,8 +25153,8 @@
       <c r="A100" s="1">
         <v>46121</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>1443</v>
+      <c r="B100" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25219,7 +25231,7 @@
       <c r="AA100" s="2" t="s">
         <v>1543</v>
       </c>
-      <c r="AB100" s="9" t="s">
+      <c r="AB100" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -25227,8 +25239,8 @@
       <c r="A101" s="1">
         <v>46122</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>1443</v>
+      <c r="B101" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25305,7 +25317,7 @@
       <c r="AA101" s="2" t="s">
         <v>1558</v>
       </c>
-      <c r="AB101" s="9" t="s">
+      <c r="AB101" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -25313,8 +25325,8 @@
       <c r="A102" s="1">
         <v>46123</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>1443</v>
+      <c r="B102" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25391,7 +25403,7 @@
       <c r="AA102" s="2" t="s">
         <v>1572</v>
       </c>
-      <c r="AB102" s="9" t="s">
+      <c r="AB102" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25399,8 +25411,8 @@
       <c r="A103" s="1">
         <v>46124</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>1443</v>
+      <c r="B103" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25477,7 +25489,7 @@
       <c r="AA103" s="2" t="s">
         <v>1588</v>
       </c>
-      <c r="AB103" s="9" t="s">
+      <c r="AB103" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25485,8 +25497,8 @@
       <c r="A104" s="1">
         <v>46125</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>1443</v>
+      <c r="B104" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25563,7 +25575,7 @@
       <c r="AA104" s="2" t="s">
         <v>1602</v>
       </c>
-      <c r="AB104" s="9" t="s">
+      <c r="AB104" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25571,8 +25583,8 @@
       <c r="A105" s="1">
         <v>46126</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>1443</v>
+      <c r="B105" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25649,7 +25661,7 @@
       <c r="AA105" s="2" t="s">
         <v>1616</v>
       </c>
-      <c r="AB105" s="9" t="s">
+      <c r="AB105" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25657,8 +25669,8 @@
       <c r="A106" s="1">
         <v>46127</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>1443</v>
+      <c r="B106" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25735,7 +25747,7 @@
       <c r="AA106" s="2" t="s">
         <v>1631</v>
       </c>
-      <c r="AB106" s="9" t="s">
+      <c r="AB106" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25743,8 +25755,8 @@
       <c r="A107" s="1">
         <v>46128</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>1443</v>
+      <c r="B107" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25821,7 +25833,7 @@
       <c r="AA107" s="2" t="s">
         <v>1645</v>
       </c>
-      <c r="AB107" s="9" t="s">
+      <c r="AB107" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25829,8 +25841,8 @@
       <c r="A108" s="1">
         <v>46129</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>1443</v>
+      <c r="B108" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25907,7 +25919,7 @@
       <c r="AA108" s="2" t="s">
         <v>1660</v>
       </c>
-      <c r="AB108" s="9" t="s">
+      <c r="AB108" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -25915,8 +25927,8 @@
       <c r="A109" s="1">
         <v>46130</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>1443</v>
+      <c r="B109" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25993,7 +26005,7 @@
       <c r="AA109" s="2" t="s">
         <v>1674</v>
       </c>
-      <c r="AB109" s="9" t="s">
+      <c r="AB109" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -26001,8 +26013,8 @@
       <c r="A110" s="1">
         <v>46131</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>1443</v>
+      <c r="B110" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26079,7 +26091,7 @@
       <c r="AA110" s="2" t="s">
         <v>1689</v>
       </c>
-      <c r="AB110" s="9" t="s">
+      <c r="AB110" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -26087,8 +26099,8 @@
       <c r="A111" s="1">
         <v>46132</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>1443</v>
+      <c r="B111" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26165,7 +26177,7 @@
       <c r="AA111" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="AB111" s="9" t="s">
+      <c r="AB111" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26173,8 +26185,8 @@
       <c r="A112" s="1">
         <v>46133</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>1443</v>
+      <c r="B112" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26251,7 +26263,7 @@
       <c r="AA112" s="2" t="s">
         <v>1720</v>
       </c>
-      <c r="AB112" s="9" t="s">
+      <c r="AB112" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26259,8 +26271,8 @@
       <c r="A113" s="1">
         <v>46134</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>1443</v>
+      <c r="B113" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26337,7 +26349,7 @@
       <c r="AA113" s="2" t="s">
         <v>1736</v>
       </c>
-      <c r="AB113" s="9" t="s">
+      <c r="AB113" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26345,8 +26357,8 @@
       <c r="A114" s="1">
         <v>46135</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>1443</v>
+      <c r="B114" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26423,7 +26435,7 @@
       <c r="AA114" s="2" t="s">
         <v>1751</v>
       </c>
-      <c r="AB114" s="9" t="s">
+      <c r="AB114" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26431,8 +26443,8 @@
       <c r="A115" s="1">
         <v>46136</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>1443</v>
+      <c r="B115" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26509,7 +26521,7 @@
       <c r="AA115" s="2" t="s">
         <v>1766</v>
       </c>
-      <c r="AB115" s="9" t="s">
+      <c r="AB115" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26517,8 +26529,8 @@
       <c r="A116" s="1">
         <v>46137</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>1443</v>
+      <c r="B116" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26595,7 +26607,7 @@
       <c r="AA116" s="2" t="s">
         <v>1780</v>
       </c>
-      <c r="AB116" s="9" t="s">
+      <c r="AB116" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26603,8 +26615,8 @@
       <c r="A117" s="1">
         <v>46138</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>1443</v>
+      <c r="B117" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26681,7 +26693,7 @@
       <c r="AA117" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="AB117" s="9" t="s">
+      <c r="AB117" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26689,8 +26701,8 @@
       <c r="A118" s="1">
         <v>46139</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>1443</v>
+      <c r="B118" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26767,7 +26779,7 @@
       <c r="AA118" s="2" t="s">
         <v>1809</v>
       </c>
-      <c r="AB118" s="9" t="s">
+      <c r="AB118" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26775,8 +26787,8 @@
       <c r="A119" s="1">
         <v>46140</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>1443</v>
+      <c r="B119" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26853,7 +26865,7 @@
       <c r="AA119" s="2" t="s">
         <v>1823</v>
       </c>
-      <c r="AB119" s="9" t="s">
+      <c r="AB119" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26861,8 +26873,8 @@
       <c r="A120" s="1">
         <v>46141</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>1443</v>
+      <c r="B120" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26939,7 +26951,7 @@
       <c r="AA120" s="2" t="s">
         <v>1837</v>
       </c>
-      <c r="AB120" s="9" t="s">
+      <c r="AB120" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -26947,8 +26959,8 @@
       <c r="A121" s="1">
         <v>46142</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>1443</v>
+      <c r="B121" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27025,7 +27037,7 @@
       <c r="AA121" s="2" t="s">
         <v>1852</v>
       </c>
-      <c r="AB121" s="9" t="s">
+      <c r="AB121" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27033,8 +27045,8 @@
       <c r="A122" s="1">
         <v>46143</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>1443</v>
+      <c r="B122" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27111,7 +27123,7 @@
       <c r="AA122" s="2" t="s">
         <v>1866</v>
       </c>
-      <c r="AB122" s="9" t="s">
+      <c r="AB122" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27119,8 +27131,8 @@
       <c r="A123" s="1">
         <v>46144</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>1867</v>
+      <c r="B123" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27197,7 +27209,7 @@
       <c r="AA123" s="2" t="s">
         <v>1882</v>
       </c>
-      <c r="AB123" s="9" t="s">
+      <c r="AB123" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27205,8 +27217,8 @@
       <c r="A124" s="1">
         <v>46145</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>1867</v>
+      <c r="B124" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27283,7 +27295,7 @@
       <c r="AA124" s="2" t="s">
         <v>1896</v>
       </c>
-      <c r="AB124" s="9" t="s">
+      <c r="AB124" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27291,8 +27303,8 @@
       <c r="A125" s="1">
         <v>46146</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>1867</v>
+      <c r="B125" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27369,7 +27381,7 @@
       <c r="AA125" s="2" t="s">
         <v>1910</v>
       </c>
-      <c r="AB125" s="9" t="s">
+      <c r="AB125" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27377,8 +27389,8 @@
       <c r="A126" s="1">
         <v>46147</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>1867</v>
+      <c r="B126" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27455,7 +27467,7 @@
       <c r="AA126" s="2" t="s">
         <v>1924</v>
       </c>
-      <c r="AB126" s="9" t="s">
+      <c r="AB126" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27463,8 +27475,8 @@
       <c r="A127" s="1">
         <v>46148</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>1867</v>
+      <c r="B127" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27541,7 +27553,7 @@
       <c r="AA127" s="2" t="s">
         <v>1938</v>
       </c>
-      <c r="AB127" s="9" t="s">
+      <c r="AB127" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27549,8 +27561,8 @@
       <c r="A128" s="1">
         <v>46149</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1867</v>
+      <c r="B128" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27627,7 +27639,7 @@
       <c r="AA128" s="2" t="s">
         <v>1953</v>
       </c>
-      <c r="AB128" s="9" t="s">
+      <c r="AB128" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27635,8 +27647,8 @@
       <c r="A129" s="1">
         <v>46150</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>1867</v>
+      <c r="B129" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27713,7 +27725,7 @@
       <c r="AA129" s="2" t="s">
         <v>1967</v>
       </c>
-      <c r="AB129" s="9" t="s">
+      <c r="AB129" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27721,8 +27733,8 @@
       <c r="A130" s="1">
         <v>46151</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>1867</v>
+      <c r="B130" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27799,7 +27811,7 @@
       <c r="AA130" s="2" t="s">
         <v>1981</v>
       </c>
-      <c r="AB130" s="9" t="s">
+      <c r="AB130" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27807,8 +27819,8 @@
       <c r="A131" s="1">
         <v>46152</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>1867</v>
+      <c r="B131" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27885,7 +27897,7 @@
       <c r="AA131" s="2" t="s">
         <v>1996</v>
       </c>
-      <c r="AB131" s="9" t="s">
+      <c r="AB131" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27893,8 +27905,8 @@
       <c r="A132" s="1">
         <v>46153</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>1867</v>
+      <c r="B132" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27971,7 +27983,7 @@
       <c r="AA132" s="2" t="s">
         <v>2010</v>
       </c>
-      <c r="AB132" s="9" t="s">
+      <c r="AB132" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -27979,8 +27991,8 @@
       <c r="A133" s="1">
         <v>46154</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>1867</v>
+      <c r="B133" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28057,7 +28069,7 @@
       <c r="AA133" s="2" t="s">
         <v>2025</v>
       </c>
-      <c r="AB133" s="9" t="s">
+      <c r="AB133" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28065,8 +28077,8 @@
       <c r="A134" s="1">
         <v>46155</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>1867</v>
+      <c r="B134" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28143,7 +28155,7 @@
       <c r="AA134" s="2" t="s">
         <v>2039</v>
       </c>
-      <c r="AB134" s="9" t="s">
+      <c r="AB134" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28151,8 +28163,8 @@
       <c r="A135" s="1">
         <v>46156</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>1867</v>
+      <c r="B135" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28229,7 +28241,7 @@
       <c r="AA135" s="2" t="s">
         <v>2053</v>
       </c>
-      <c r="AB135" s="9" t="s">
+      <c r="AB135" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28237,8 +28249,8 @@
       <c r="A136" s="1">
         <v>46157</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>1867</v>
+      <c r="B136" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28315,7 +28327,7 @@
       <c r="AA136" s="2" t="s">
         <v>2069</v>
       </c>
-      <c r="AB136" s="9" t="s">
+      <c r="AB136" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28323,8 +28335,8 @@
       <c r="A137" s="1">
         <v>46158</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>1867</v>
+      <c r="B137" s="9" t="s">
+        <v>2304</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28401,7 +28413,7 @@
       <c r="AA137" s="2" t="s">
         <v>2084</v>
       </c>
-      <c r="AB137" s="9" t="s">
+      <c r="AB137" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28409,8 +28421,8 @@
       <c r="A138" s="1">
         <v>46159</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>1867</v>
+      <c r="B138" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28487,7 +28499,7 @@
       <c r="AA138" s="2" t="s">
         <v>2099</v>
       </c>
-      <c r="AB138" s="9" t="s">
+      <c r="AB138" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28495,8 +28507,8 @@
       <c r="A139" s="1">
         <v>46160</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>1867</v>
+      <c r="B139" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28573,7 +28585,7 @@
       <c r="AA139" s="2" t="s">
         <v>2114</v>
       </c>
-      <c r="AB139" s="9" t="s">
+      <c r="AB139" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28581,8 +28593,8 @@
       <c r="A140" s="1">
         <v>46161</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>1867</v>
+      <c r="B140" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28659,7 +28671,7 @@
       <c r="AA140" s="2" t="s">
         <v>2128</v>
       </c>
-      <c r="AB140" s="9" t="s">
+      <c r="AB140" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28667,8 +28679,8 @@
       <c r="A141" s="1">
         <v>46162</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>1867</v>
+      <c r="B141" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28745,7 +28757,7 @@
       <c r="AA141" s="2" t="s">
         <v>2144</v>
       </c>
-      <c r="AB141" s="9" t="s">
+      <c r="AB141" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28753,8 +28765,8 @@
       <c r="A142" s="1">
         <v>46163</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>1867</v>
+      <c r="B142" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28831,7 +28843,7 @@
       <c r="AA142" s="2" t="s">
         <v>2158</v>
       </c>
-      <c r="AB142" s="9" t="s">
+      <c r="AB142" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28839,8 +28851,8 @@
       <c r="A143" s="1">
         <v>46164</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>1867</v>
+      <c r="B143" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28917,7 +28929,7 @@
       <c r="AA143" s="2" t="s">
         <v>2172</v>
       </c>
-      <c r="AB143" s="9" t="s">
+      <c r="AB143" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -28925,8 +28937,8 @@
       <c r="A144" s="1">
         <v>46165</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>1867</v>
+      <c r="B144" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29003,7 +29015,7 @@
       <c r="AA144" s="2" t="s">
         <v>2186</v>
       </c>
-      <c r="AB144" s="9" t="s">
+      <c r="AB144" s="2" t="s">
         <v>2187</v>
       </c>
     </row>
@@ -29011,8 +29023,8 @@
       <c r="A145" s="1">
         <v>46166</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>1867</v>
+      <c r="B145" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29089,7 +29101,7 @@
       <c r="AA145" s="2" t="s">
         <v>2201</v>
       </c>
-      <c r="AB145" s="9" t="s">
+      <c r="AB145" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29097,8 +29109,8 @@
       <c r="A146" s="1">
         <v>46167</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>1867</v>
+      <c r="B146" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29175,7 +29187,7 @@
       <c r="AA146" s="2" t="s">
         <v>2216</v>
       </c>
-      <c r="AB146" s="9" t="s">
+      <c r="AB146" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29183,8 +29195,8 @@
       <c r="A147" s="1">
         <v>46168</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>1867</v>
+      <c r="B147" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29261,7 +29273,7 @@
       <c r="AA147" s="2" t="s">
         <v>2230</v>
       </c>
-      <c r="AB147" s="9" t="s">
+      <c r="AB147" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29269,8 +29281,8 @@
       <c r="A148" s="1">
         <v>46169</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>1867</v>
+      <c r="B148" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29347,7 +29359,7 @@
       <c r="AA148" s="2" t="s">
         <v>2246</v>
       </c>
-      <c r="AB148" s="9" t="s">
+      <c r="AB148" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29355,8 +29367,8 @@
       <c r="A149" s="1">
         <v>46170</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>1867</v>
+      <c r="B149" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29433,7 +29445,7 @@
       <c r="AA149" s="2" t="s">
         <v>2260</v>
       </c>
-      <c r="AB149" s="9" t="s">
+      <c r="AB149" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29441,8 +29453,8 @@
       <c r="A150" s="1">
         <v>46171</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>1867</v>
+      <c r="B150" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29519,7 +29531,7 @@
       <c r="AA150" s="2" t="s">
         <v>2274</v>
       </c>
-      <c r="AB150" s="9" t="s">
+      <c r="AB150" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29527,8 +29539,8 @@
       <c r="A151" s="1">
         <v>46172</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>1867</v>
+      <c r="B151" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29605,7 +29617,7 @@
       <c r="AA151" s="2" t="s">
         <v>2289</v>
       </c>
-      <c r="AB151" s="9" t="s">
+      <c r="AB151" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29613,8 +29625,8 @@
       <c r="A152" s="1">
         <v>46173</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>1867</v>
+      <c r="B152" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29691,7 +29703,7 @@
       <c r="AA152" s="2" t="s">
         <v>2303</v>
       </c>
-      <c r="AB152" s="9" t="s">
+      <c r="AB152" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29699,8 +29711,8 @@
       <c r="A153" s="1">
         <v>46174</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>2304</v>
+      <c r="B153" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29777,7 +29789,7 @@
       <c r="AA153" s="2" t="s">
         <v>2318</v>
       </c>
-      <c r="AB153" s="9" t="s">
+      <c r="AB153" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29785,8 +29797,8 @@
       <c r="A154" s="1">
         <v>46175</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>2304</v>
+      <c r="B154" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29863,7 +29875,7 @@
       <c r="AA154" s="2" t="s">
         <v>2332</v>
       </c>
-      <c r="AB154" s="9" t="s">
+      <c r="AB154" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29871,8 +29883,8 @@
       <c r="A155" s="1">
         <v>46176</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>2304</v>
+      <c r="B155" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29949,7 +29961,7 @@
       <c r="AA155" s="2" t="s">
         <v>2346</v>
       </c>
-      <c r="AB155" s="9" t="s">
+      <c r="AB155" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -29957,8 +29969,8 @@
       <c r="A156" s="1">
         <v>46177</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>2304</v>
+      <c r="B156" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30035,7 +30047,7 @@
       <c r="AA156" s="2" t="s">
         <v>2361</v>
       </c>
-      <c r="AB156" s="9" t="s">
+      <c r="AB156" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30043,8 +30055,8 @@
       <c r="A157" s="1">
         <v>46178</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>2304</v>
+      <c r="B157" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30121,7 +30133,7 @@
       <c r="AA157" s="2" t="s">
         <v>2374</v>
       </c>
-      <c r="AB157" s="9" t="s">
+      <c r="AB157" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30129,8 +30141,8 @@
       <c r="A158" s="1">
         <v>46179</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>2304</v>
+      <c r="B158" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30207,7 +30219,7 @@
       <c r="AA158" s="2" t="s">
         <v>2389</v>
       </c>
-      <c r="AB158" s="9" t="s">
+      <c r="AB158" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30215,8 +30227,8 @@
       <c r="A159" s="1">
         <v>46180</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>2304</v>
+      <c r="B159" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30293,7 +30305,7 @@
       <c r="AA159" s="2" t="s">
         <v>2403</v>
       </c>
-      <c r="AB159" s="9" t="s">
+      <c r="AB159" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30301,8 +30313,8 @@
       <c r="A160" s="1">
         <v>46181</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>2304</v>
+      <c r="B160" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30379,7 +30391,7 @@
       <c r="AA160" s="2" t="s">
         <v>2419</v>
       </c>
-      <c r="AB160" s="9" t="s">
+      <c r="AB160" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30387,8 +30399,8 @@
       <c r="A161" s="1">
         <v>46182</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>2304</v>
+      <c r="B161" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30465,7 +30477,7 @@
       <c r="AA161" s="2" t="s">
         <v>2433</v>
       </c>
-      <c r="AB161" s="9" t="s">
+      <c r="AB161" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30473,8 +30485,8 @@
       <c r="A162" s="1">
         <v>46183</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>2304</v>
+      <c r="B162" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30551,7 +30563,7 @@
       <c r="AA162" s="2" t="s">
         <v>2447</v>
       </c>
-      <c r="AB162" s="9" t="s">
+      <c r="AB162" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30559,8 +30571,8 @@
       <c r="A163" s="1">
         <v>46184</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>2304</v>
+      <c r="B163" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30637,7 +30649,7 @@
       <c r="AA163" s="2" t="s">
         <v>2462</v>
       </c>
-      <c r="AB163" s="9" t="s">
+      <c r="AB163" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30645,8 +30657,8 @@
       <c r="A164" s="1">
         <v>46185</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>2304</v>
+      <c r="B164" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30723,7 +30735,7 @@
       <c r="AA164" s="2" t="s">
         <v>2476</v>
       </c>
-      <c r="AB164" s="9" t="s">
+      <c r="AB164" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30731,8 +30743,8 @@
       <c r="A165" s="1">
         <v>46186</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>2304</v>
+      <c r="B165" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30809,7 +30821,7 @@
       <c r="AA165" s="2" t="s">
         <v>2491</v>
       </c>
-      <c r="AB165" s="9" t="s">
+      <c r="AB165" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30817,8 +30829,8 @@
       <c r="A166" s="1">
         <v>46187</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>2304</v>
+      <c r="B166" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30895,7 +30907,7 @@
       <c r="AA166" s="2" t="s">
         <v>2504</v>
       </c>
-      <c r="AB166" s="9" t="s">
+      <c r="AB166" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30903,8 +30915,8 @@
       <c r="A167" s="1">
         <v>46188</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>2304</v>
+      <c r="B167" s="9" t="s">
+        <v>5399</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
@@ -30981,7 +30993,7 @@
       <c r="AA167" s="2" t="s">
         <v>2519</v>
       </c>
-      <c r="AB167" s="9" t="s">
+      <c r="AB167" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -30989,7 +31001,7 @@
       <c r="A168" s="1">
         <v>46189</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -31067,7 +31079,7 @@
       <c r="AA168" s="2" t="s">
         <v>2536</v>
       </c>
-      <c r="AB168" s="9" t="s">
+      <c r="AB168" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31075,7 +31087,7 @@
       <c r="A169" s="1">
         <v>46190</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C169" s="2" t="s">
@@ -31153,7 +31165,7 @@
       <c r="AA169" s="2" t="s">
         <v>2551</v>
       </c>
-      <c r="AB169" s="9" t="s">
+      <c r="AB169" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31161,7 +31173,7 @@
       <c r="A170" s="1">
         <v>46191</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -31239,7 +31251,7 @@
       <c r="AA170" s="2" t="s">
         <v>2565</v>
       </c>
-      <c r="AB170" s="9" t="s">
+      <c r="AB170" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31247,7 +31259,7 @@
       <c r="A171" s="1">
         <v>46192</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C171" s="2" t="s">
@@ -31325,7 +31337,7 @@
       <c r="AA171" s="2" t="s">
         <v>2579</v>
       </c>
-      <c r="AB171" s="9" t="s">
+      <c r="AB171" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31333,7 +31345,7 @@
       <c r="A172" s="1">
         <v>46193</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -31411,7 +31423,7 @@
       <c r="AA172" s="2" t="s">
         <v>2593</v>
       </c>
-      <c r="AB172" s="9" t="s">
+      <c r="AB172" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31419,7 +31431,7 @@
       <c r="A173" s="1">
         <v>46194</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B173" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -31497,7 +31509,7 @@
       <c r="AA173" s="2" t="s">
         <v>2608</v>
       </c>
-      <c r="AB173" s="9" t="s">
+      <c r="AB173" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31505,7 +31517,7 @@
       <c r="A174" s="1">
         <v>46195</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B174" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C174" s="2" t="s">
@@ -31583,7 +31595,7 @@
       <c r="AA174" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="AB174" s="9" t="s">
+      <c r="AB174" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -31591,7 +31603,7 @@
       <c r="A175" s="1">
         <v>46196</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -31669,7 +31681,7 @@
       <c r="AA175" s="2" t="s">
         <v>2635</v>
       </c>
-      <c r="AB175" s="9" t="s">
+      <c r="AB175" s="2" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -31677,7 +31689,7 @@
       <c r="A176" s="1">
         <v>46197</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B176" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -31755,7 +31767,7 @@
       <c r="AA176" s="2" t="s">
         <v>2650</v>
       </c>
-      <c r="AB176" s="9" t="s">
+      <c r="AB176" s="2" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -31763,7 +31775,7 @@
       <c r="A177" s="1">
         <v>46198</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B177" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -31841,7 +31853,7 @@
       <c r="AA177" s="2" t="s">
         <v>2664</v>
       </c>
-      <c r="AB177" s="9" t="s">
+      <c r="AB177" s="2" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -31849,7 +31861,7 @@
       <c r="A178" s="1">
         <v>46199</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C178" s="2" t="s">
@@ -31927,7 +31939,7 @@
       <c r="AA178" s="2" t="s">
         <v>2679</v>
       </c>
-      <c r="AB178" s="9" t="s">
+      <c r="AB178" s="2" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -31935,7 +31947,7 @@
       <c r="A179" s="1">
         <v>46200</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B179" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C179" s="2" t="s">
@@ -32013,7 +32025,7 @@
       <c r="AA179" s="2" t="s">
         <v>2693</v>
       </c>
-      <c r="AB179" s="9" t="s">
+      <c r="AB179" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32021,7 +32033,7 @@
       <c r="A180" s="1">
         <v>46201</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C180" s="2" t="s">
@@ -32099,7 +32111,7 @@
       <c r="AA180" s="2" t="s">
         <v>2708</v>
       </c>
-      <c r="AB180" s="9" t="s">
+      <c r="AB180" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32107,7 +32119,7 @@
       <c r="A181" s="1">
         <v>46202</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="9" t="s">
         <v>2304</v>
       </c>
       <c r="C181" s="2" t="s">
@@ -32185,7 +32197,7 @@
       <c r="AA181" s="2" t="s">
         <v>2722</v>
       </c>
-      <c r="AB181" s="9" t="s">
+      <c r="AB181" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32193,7 +32205,7 @@
       <c r="A182" s="1">
         <v>46203</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -32271,7 +32283,7 @@
       <c r="AA182" s="2" t="s">
         <v>2737</v>
       </c>
-      <c r="AB182" s="9" t="s">
+      <c r="AB182" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32279,7 +32291,7 @@
       <c r="A183" s="1">
         <v>46204</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C183" s="2" t="s">
@@ -32357,7 +32369,7 @@
       <c r="AA183" s="2" t="s">
         <v>2752</v>
       </c>
-      <c r="AB183" s="9" t="s">
+      <c r="AB183" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32365,7 +32377,7 @@
       <c r="A184" s="1">
         <v>46205</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B184" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C184" s="2" t="s">
@@ -32443,7 +32455,7 @@
       <c r="AA184" s="2" t="s">
         <v>2765</v>
       </c>
-      <c r="AB184" s="9" t="s">
+      <c r="AB184" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32451,7 +32463,7 @@
       <c r="A185" s="1">
         <v>46206</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C185" s="2" t="s">
@@ -32529,7 +32541,7 @@
       <c r="AA185" s="2" t="s">
         <v>2780</v>
       </c>
-      <c r="AB185" s="9" t="s">
+      <c r="AB185" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32537,7 +32549,7 @@
       <c r="A186" s="1">
         <v>46207</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C186" s="2" t="s">
@@ -32615,7 +32627,7 @@
       <c r="AA186" s="2" t="s">
         <v>2794</v>
       </c>
-      <c r="AB186" s="9" t="s">
+      <c r="AB186" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32623,7 +32635,7 @@
       <c r="A187" s="1">
         <v>46208</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C187" s="2" t="s">
@@ -32701,7 +32713,7 @@
       <c r="AA187" s="2" t="s">
         <v>2807</v>
       </c>
-      <c r="AB187" s="9" t="s">
+      <c r="AB187" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32709,7 +32721,7 @@
       <c r="A188" s="1">
         <v>46209</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -32787,7 +32799,7 @@
       <c r="AA188" s="2" t="s">
         <v>2821</v>
       </c>
-      <c r="AB188" s="9" t="s">
+      <c r="AB188" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32795,7 +32807,7 @@
       <c r="A189" s="1">
         <v>46210</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -32873,7 +32885,7 @@
       <c r="AA189" s="2" t="s">
         <v>2834</v>
       </c>
-      <c r="AB189" s="9" t="s">
+      <c r="AB189" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32881,7 +32893,7 @@
       <c r="A190" s="1">
         <v>46211</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C190" s="2" t="s">
@@ -32959,7 +32971,7 @@
       <c r="AA190" s="2" t="s">
         <v>2847</v>
       </c>
-      <c r="AB190" s="9" t="s">
+      <c r="AB190" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -32967,7 +32979,7 @@
       <c r="A191" s="1">
         <v>46212</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B191" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C191" s="2" t="s">
@@ -33045,7 +33057,7 @@
       <c r="AA191" s="2" t="s">
         <v>2864</v>
       </c>
-      <c r="AB191" s="9" t="s">
+      <c r="AB191" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -33053,7 +33065,7 @@
       <c r="A192" s="1">
         <v>46213</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C192" s="2" t="s">
@@ -33131,7 +33143,7 @@
       <c r="AA192" s="2" t="s">
         <v>2879</v>
       </c>
-      <c r="AB192" s="9" t="s">
+      <c r="AB192" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -33139,7 +33151,7 @@
       <c r="A193" s="1">
         <v>46214</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -33217,7 +33229,7 @@
       <c r="AA193" s="2" t="s">
         <v>2893</v>
       </c>
-      <c r="AB193" s="9" t="s">
+      <c r="AB193" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -33225,7 +33237,7 @@
       <c r="A194" s="1">
         <v>46215</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C194" s="2" t="s">
@@ -33303,7 +33315,7 @@
       <c r="AA194" s="2" t="s">
         <v>2909</v>
       </c>
-      <c r="AB194" s="9" t="s">
+      <c r="AB194" s="2" t="s">
         <v>2694</v>
       </c>
     </row>
@@ -33311,7 +33323,7 @@
       <c r="A195" s="1">
         <v>46216</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -33389,7 +33401,7 @@
       <c r="AA195" s="2" t="s">
         <v>2924</v>
       </c>
-      <c r="AB195" s="9" t="s">
+      <c r="AB195" s="2" t="s">
         <v>2636</v>
       </c>
     </row>
@@ -33397,7 +33409,7 @@
       <c r="A196" s="1">
         <v>46217</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -33475,7 +33487,7 @@
       <c r="AA196" s="2" t="s">
         <v>2939</v>
       </c>
-      <c r="AB196" s="9" t="s">
+      <c r="AB196" s="2" t="s">
         <v>2940</v>
       </c>
     </row>
@@ -33483,7 +33495,7 @@
       <c r="A197" s="1">
         <v>46218</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C197" s="2" t="s">
@@ -33561,7 +33573,7 @@
       <c r="AA197" s="2" t="s">
         <v>2954</v>
       </c>
-      <c r="AB197" s="9" t="s">
+      <c r="AB197" s="2" t="s">
         <v>2940</v>
       </c>
     </row>
@@ -33569,7 +33581,7 @@
       <c r="A198" s="1">
         <v>46219</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -33647,7 +33659,7 @@
       <c r="AA198" s="2" t="s">
         <v>2968</v>
       </c>
-      <c r="AB198" s="9" t="s">
+      <c r="AB198" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -33655,7 +33667,7 @@
       <c r="A199" s="1">
         <v>46220</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -33733,7 +33745,7 @@
       <c r="AA199" s="2" t="s">
         <v>2984</v>
       </c>
-      <c r="AB199" s="9" t="s">
+      <c r="AB199" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -33741,7 +33753,7 @@
       <c r="A200" s="1">
         <v>46221</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -33819,7 +33831,7 @@
       <c r="AA200" s="2" t="s">
         <v>2999</v>
       </c>
-      <c r="AB200" s="9" t="s">
+      <c r="AB200" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -33827,7 +33839,7 @@
       <c r="A201" s="1">
         <v>46222</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B201" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -33905,7 +33917,7 @@
       <c r="AA201" s="2" t="s">
         <v>3013</v>
       </c>
-      <c r="AB201" s="9" t="s">
+      <c r="AB201" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -33913,7 +33925,7 @@
       <c r="A202" s="1">
         <v>46223</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B202" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C202" s="2" t="s">
@@ -33991,7 +34003,7 @@
       <c r="AA202" s="2" t="s">
         <v>3027</v>
       </c>
-      <c r="AB202" s="9" t="s">
+      <c r="AB202" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -33999,7 +34011,7 @@
       <c r="A203" s="1">
         <v>46224</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -34077,7 +34089,7 @@
       <c r="AA203" s="2" t="s">
         <v>3041</v>
       </c>
-      <c r="AB203" s="9" t="s">
+      <c r="AB203" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -34085,7 +34097,7 @@
       <c r="A204" s="1">
         <v>46225</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="B204" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -34163,7 +34175,7 @@
       <c r="AA204" s="2" t="s">
         <v>3054</v>
       </c>
-      <c r="AB204" s="9" t="s">
+      <c r="AB204" s="2" t="s">
         <v>2969</v>
       </c>
     </row>
@@ -34171,7 +34183,7 @@
       <c r="A205" s="1">
         <v>46226</v>
       </c>
-      <c r="B205" s="2" t="s">
+      <c r="B205" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -34249,7 +34261,7 @@
       <c r="AA205" s="2" t="s">
         <v>3069</v>
       </c>
-      <c r="AB205" s="9" t="s">
+      <c r="AB205" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34257,7 +34269,7 @@
       <c r="A206" s="1">
         <v>46227</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C206" s="2" t="s">
@@ -34335,7 +34347,7 @@
       <c r="AA206" s="2" t="s">
         <v>3084</v>
       </c>
-      <c r="AB206" s="9" t="s">
+      <c r="AB206" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34343,7 +34355,7 @@
       <c r="A207" s="1">
         <v>46228</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C207" s="2" t="s">
@@ -34421,7 +34433,7 @@
       <c r="AA207" s="2" t="s">
         <v>3098</v>
       </c>
-      <c r="AB207" s="9" t="s">
+      <c r="AB207" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34429,7 +34441,7 @@
       <c r="A208" s="1">
         <v>46229</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -34507,7 +34519,7 @@
       <c r="AA208" s="2" t="s">
         <v>3112</v>
       </c>
-      <c r="AB208" s="9" t="s">
+      <c r="AB208" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34515,7 +34527,7 @@
       <c r="A209" s="1">
         <v>46230</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C209" s="2" t="s">
@@ -34593,7 +34605,7 @@
       <c r="AA209" s="2" t="s">
         <v>3126</v>
       </c>
-      <c r="AB209" s="9" t="s">
+      <c r="AB209" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34601,7 +34613,7 @@
       <c r="A210" s="1">
         <v>46231</v>
       </c>
-      <c r="B210" s="2" t="s">
+      <c r="B210" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -34679,7 +34691,7 @@
       <c r="AA210" s="2" t="s">
         <v>3140</v>
       </c>
-      <c r="AB210" s="9" t="s">
+      <c r="AB210" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34687,7 +34699,7 @@
       <c r="A211" s="1">
         <v>46232</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B211" s="10" t="s">
         <v>2723</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -34765,7 +34777,7 @@
       <c r="AA211" s="2" t="s">
         <v>3154</v>
       </c>
-      <c r="AB211" s="9" t="s">
+      <c r="AB211" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34773,7 +34785,7 @@
       <c r="A212" s="1">
         <v>46233</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -34851,7 +34863,7 @@
       <c r="AA212" s="2" t="s">
         <v>3169</v>
       </c>
-      <c r="AB212" s="9" t="s">
+      <c r="AB212" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34859,7 +34871,7 @@
       <c r="A213" s="1">
         <v>46234</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="B213" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C213" s="2" t="s">
@@ -34937,7 +34949,7 @@
       <c r="AA213" s="2" t="s">
         <v>3184</v>
       </c>
-      <c r="AB213" s="9" t="s">
+      <c r="AB213" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -34945,7 +34957,7 @@
       <c r="A214" s="1">
         <v>46235</v>
       </c>
-      <c r="B214" s="2" t="s">
+      <c r="B214" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -35023,7 +35035,7 @@
       <c r="AA214" s="2" t="s">
         <v>3198</v>
       </c>
-      <c r="AB214" s="9" t="s">
+      <c r="AB214" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35031,7 +35043,7 @@
       <c r="A215" s="1">
         <v>46236</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B215" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -35109,7 +35121,7 @@
       <c r="AA215" s="2" t="s">
         <v>3213</v>
       </c>
-      <c r="AB215" s="9" t="s">
+      <c r="AB215" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35117,7 +35129,7 @@
       <c r="A216" s="1">
         <v>46237</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B216" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C216" s="2" t="s">
@@ -35195,7 +35207,7 @@
       <c r="AA216" s="2" t="s">
         <v>3227</v>
       </c>
-      <c r="AB216" s="9" t="s">
+      <c r="AB216" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35203,7 +35215,7 @@
       <c r="A217" s="1">
         <v>46238</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="B217" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C217" s="2" t="s">
@@ -35281,7 +35293,7 @@
       <c r="AA217" s="2" t="s">
         <v>3241</v>
       </c>
-      <c r="AB217" s="9" t="s">
+      <c r="AB217" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35289,7 +35301,7 @@
       <c r="A218" s="1">
         <v>46239</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C218" s="2" t="s">
@@ -35367,7 +35379,7 @@
       <c r="AA218" s="2" t="s">
         <v>3256</v>
       </c>
-      <c r="AB218" s="9" t="s">
+      <c r="AB218" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35375,7 +35387,7 @@
       <c r="A219" s="1">
         <v>46240</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -35453,7 +35465,7 @@
       <c r="AA219" s="2" t="s">
         <v>3271</v>
       </c>
-      <c r="AB219" s="9" t="s">
+      <c r="AB219" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35461,7 +35473,7 @@
       <c r="A220" s="1">
         <v>46241</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C220" s="2" t="s">
@@ -35539,7 +35551,7 @@
       <c r="AA220" s="2" t="s">
         <v>3285</v>
       </c>
-      <c r="AB220" s="9" t="s">
+      <c r="AB220" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35547,7 +35559,7 @@
       <c r="A221" s="1">
         <v>46242</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C221" s="2" t="s">
@@ -35625,7 +35637,7 @@
       <c r="AA221" s="2" t="s">
         <v>3301</v>
       </c>
-      <c r="AB221" s="9" t="s">
+      <c r="AB221" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35633,7 +35645,7 @@
       <c r="A222" s="1">
         <v>46243</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -35711,7 +35723,7 @@
       <c r="AA222" s="2" t="s">
         <v>3315</v>
       </c>
-      <c r="AB222" s="9" t="s">
+      <c r="AB222" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35719,7 +35731,7 @@
       <c r="A223" s="1">
         <v>46244</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C223" s="2" t="s">
@@ -35797,7 +35809,7 @@
       <c r="AA223" s="2" t="s">
         <v>3331</v>
       </c>
-      <c r="AB223" s="9" t="s">
+      <c r="AB223" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35805,7 +35817,7 @@
       <c r="A224" s="1">
         <v>46245</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C224" s="2" t="s">
@@ -35883,7 +35895,7 @@
       <c r="AA224" s="2" t="s">
         <v>3345</v>
       </c>
-      <c r="AB224" s="9" t="s">
+      <c r="AB224" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35891,7 +35903,7 @@
       <c r="A225" s="1">
         <v>46246</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C225" s="2" t="s">
@@ -35969,7 +35981,7 @@
       <c r="AA225" s="2" t="s">
         <v>3359</v>
       </c>
-      <c r="AB225" s="9" t="s">
+      <c r="AB225" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -35977,7 +35989,7 @@
       <c r="A226" s="1">
         <v>46247</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C226" s="2" t="s">
@@ -36055,7 +36067,7 @@
       <c r="AA226" s="2" t="s">
         <v>3373</v>
       </c>
-      <c r="AB226" s="9" t="s">
+      <c r="AB226" s="2" t="s">
         <v>3070</v>
       </c>
     </row>
@@ -36063,7 +36075,7 @@
       <c r="A227" s="1">
         <v>46248</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -36141,7 +36153,7 @@
       <c r="AA227" s="2" t="s">
         <v>3387</v>
       </c>
-      <c r="AB227" s="9" t="s">
+      <c r="AB227" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -36149,7 +36161,7 @@
       <c r="A228" s="1">
         <v>46249</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C228" s="2" t="s">
@@ -36227,7 +36239,7 @@
       <c r="AA228" s="2" t="s">
         <v>3403</v>
       </c>
-      <c r="AB228" s="9" t="s">
+      <c r="AB228" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -36235,7 +36247,7 @@
       <c r="A229" s="1">
         <v>46250</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C229" s="2" t="s">
@@ -36313,7 +36325,7 @@
       <c r="AA229" s="2" t="s">
         <v>3416</v>
       </c>
-      <c r="AB229" s="9" t="s">
+      <c r="AB229" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36321,7 +36333,7 @@
       <c r="A230" s="1">
         <v>46251</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -36399,7 +36411,7 @@
       <c r="AA230" s="2" t="s">
         <v>3432</v>
       </c>
-      <c r="AB230" s="9" t="s">
+      <c r="AB230" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36407,7 +36419,7 @@
       <c r="A231" s="1">
         <v>46252</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -36485,7 +36497,7 @@
       <c r="AA231" s="2" t="s">
         <v>3446</v>
       </c>
-      <c r="AB231" s="9" t="s">
+      <c r="AB231" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36493,7 +36505,7 @@
       <c r="A232" s="1">
         <v>46253</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C232" s="2" t="s">
@@ -36571,7 +36583,7 @@
       <c r="AA232" s="2" t="s">
         <v>3461</v>
       </c>
-      <c r="AB232" s="9" t="s">
+      <c r="AB232" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36579,7 +36591,7 @@
       <c r="A233" s="1">
         <v>46254</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C233" s="2" t="s">
@@ -36657,7 +36669,7 @@
       <c r="AA233" s="2" t="s">
         <v>3475</v>
       </c>
-      <c r="AB233" s="9" t="s">
+      <c r="AB233" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36665,7 +36677,7 @@
       <c r="A234" s="1">
         <v>46255</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C234" s="2" t="s">
@@ -36743,7 +36755,7 @@
       <c r="AA234" s="2" t="s">
         <v>3489</v>
       </c>
-      <c r="AB234" s="9" t="s">
+      <c r="AB234" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36751,7 +36763,7 @@
       <c r="A235" s="1">
         <v>46256</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C235" s="2" t="s">
@@ -36829,7 +36841,7 @@
       <c r="AA235" s="2" t="s">
         <v>3503</v>
       </c>
-      <c r="AB235" s="9" t="s">
+      <c r="AB235" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36837,7 +36849,7 @@
       <c r="A236" s="1">
         <v>46257</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="B236" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C236" s="2" t="s">
@@ -36915,7 +36927,7 @@
       <c r="AA236" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="AB236" s="9" t="s">
+      <c r="AB236" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -36923,7 +36935,7 @@
       <c r="A237" s="1">
         <v>46258</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B237" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C237" s="2" t="s">
@@ -37001,7 +37013,7 @@
       <c r="AA237" s="2" t="s">
         <v>3532</v>
       </c>
-      <c r="AB237" s="9" t="s">
+      <c r="AB237" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37009,7 +37021,7 @@
       <c r="A238" s="1">
         <v>46259</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C238" s="2" t="s">
@@ -37087,7 +37099,7 @@
       <c r="AA238" s="2" t="s">
         <v>3546</v>
       </c>
-      <c r="AB238" s="9" t="s">
+      <c r="AB238" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37095,7 +37107,7 @@
       <c r="A239" s="1">
         <v>46260</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="B239" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -37173,7 +37185,7 @@
       <c r="AA239" s="2" t="s">
         <v>3559</v>
       </c>
-      <c r="AB239" s="9" t="s">
+      <c r="AB239" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37181,7 +37193,7 @@
       <c r="A240" s="1">
         <v>46261</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -37259,7 +37271,7 @@
       <c r="AA240" s="2" t="s">
         <v>3574</v>
       </c>
-      <c r="AB240" s="9" t="s">
+      <c r="AB240" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37267,7 +37279,7 @@
       <c r="A241" s="1">
         <v>46262</v>
       </c>
-      <c r="B241" s="2" t="s">
+      <c r="B241" s="10" t="s">
         <v>3155</v>
       </c>
       <c r="C241" s="2" t="s">
@@ -37345,7 +37357,7 @@
       <c r="AA241" s="2" t="s">
         <v>3588</v>
       </c>
-      <c r="AB241" s="9" t="s">
+      <c r="AB241" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37353,7 +37365,7 @@
       <c r="A242" s="1">
         <v>46263</v>
       </c>
-      <c r="B242" s="2" t="s">
+      <c r="B242" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -37431,7 +37443,7 @@
       <c r="AA242" s="2" t="s">
         <v>3604</v>
       </c>
-      <c r="AB242" s="9" t="s">
+      <c r="AB242" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37439,7 +37451,7 @@
       <c r="A243" s="1">
         <v>46264</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -37517,7 +37529,7 @@
       <c r="AA243" s="2" t="s">
         <v>3619</v>
       </c>
-      <c r="AB243" s="9" t="s">
+      <c r="AB243" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37525,7 +37537,7 @@
       <c r="A244" s="1">
         <v>46265</v>
       </c>
-      <c r="B244" s="2" t="s">
+      <c r="B244" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -37603,7 +37615,7 @@
       <c r="AA244" s="2" t="s">
         <v>3632</v>
       </c>
-      <c r="AB244" s="9" t="s">
+      <c r="AB244" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37611,7 +37623,7 @@
       <c r="A245" s="1">
         <v>46266</v>
       </c>
-      <c r="B245" s="2" t="s">
+      <c r="B245" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C245" s="2" t="s">
@@ -37689,7 +37701,7 @@
       <c r="AA245" s="2" t="s">
         <v>3648</v>
       </c>
-      <c r="AB245" s="9" t="s">
+      <c r="AB245" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37697,7 +37709,7 @@
       <c r="A246" s="1">
         <v>46267</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="B246" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C246" s="2" t="s">
@@ -37775,7 +37787,7 @@
       <c r="AA246" s="2" t="s">
         <v>3662</v>
       </c>
-      <c r="AB246" s="9" t="s">
+      <c r="AB246" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37783,7 +37795,7 @@
       <c r="A247" s="1">
         <v>46268</v>
       </c>
-      <c r="B247" s="2" t="s">
+      <c r="B247" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -37861,7 +37873,7 @@
       <c r="AA247" s="2" t="s">
         <v>3677</v>
       </c>
-      <c r="AB247" s="9" t="s">
+      <c r="AB247" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37869,7 +37881,7 @@
       <c r="A248" s="1">
         <v>46269</v>
       </c>
-      <c r="B248" s="2" t="s">
+      <c r="B248" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C248" s="2" t="s">
@@ -37947,7 +37959,7 @@
       <c r="AA248" s="2" t="s">
         <v>3690</v>
       </c>
-      <c r="AB248" s="9" t="s">
+      <c r="AB248" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -37955,7 +37967,7 @@
       <c r="A249" s="1">
         <v>46270</v>
       </c>
-      <c r="B249" s="2" t="s">
+      <c r="B249" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C249" s="2" t="s">
@@ -38033,7 +38045,7 @@
       <c r="AA249" s="2" t="s">
         <v>3705</v>
       </c>
-      <c r="AB249" s="9" t="s">
+      <c r="AB249" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38041,7 +38053,7 @@
       <c r="A250" s="1">
         <v>46271</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="B250" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C250" s="2" t="s">
@@ -38119,7 +38131,7 @@
       <c r="AA250" s="2" t="s">
         <v>3720</v>
       </c>
-      <c r="AB250" s="9" t="s">
+      <c r="AB250" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38127,7 +38139,7 @@
       <c r="A251" s="1">
         <v>46272</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="B251" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C251" s="2" t="s">
@@ -38205,7 +38217,7 @@
       <c r="AA251" s="2" t="s">
         <v>3736</v>
       </c>
-      <c r="AB251" s="9" t="s">
+      <c r="AB251" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38213,7 +38225,7 @@
       <c r="A252" s="1">
         <v>46273</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="B252" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C252" s="2" t="s">
@@ -38291,7 +38303,7 @@
       <c r="AA252" s="2" t="s">
         <v>3750</v>
       </c>
-      <c r="AB252" s="9" t="s">
+      <c r="AB252" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38299,7 +38311,7 @@
       <c r="A253" s="1">
         <v>46274</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="B253" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C253" s="2" t="s">
@@ -38377,7 +38389,7 @@
       <c r="AA253" s="2" t="s">
         <v>3764</v>
       </c>
-      <c r="AB253" s="9" t="s">
+      <c r="AB253" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38385,7 +38397,7 @@
       <c r="A254" s="1">
         <v>46275</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="B254" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C254" s="2" t="s">
@@ -38463,7 +38475,7 @@
       <c r="AA254" s="2" t="s">
         <v>3778</v>
       </c>
-      <c r="AB254" s="9" t="s">
+      <c r="AB254" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38471,7 +38483,7 @@
       <c r="A255" s="1">
         <v>46276</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="B255" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -38549,7 +38561,7 @@
       <c r="AA255" s="2" t="s">
         <v>3793</v>
       </c>
-      <c r="AB255" s="9" t="s">
+      <c r="AB255" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38557,7 +38569,7 @@
       <c r="A256" s="1">
         <v>46277</v>
       </c>
-      <c r="B256" s="2" t="s">
+      <c r="B256" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C256" s="2" t="s">
@@ -38635,7 +38647,7 @@
       <c r="AA256" s="2" t="s">
         <v>3807</v>
       </c>
-      <c r="AB256" s="9" t="s">
+      <c r="AB256" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38643,7 +38655,7 @@
       <c r="A257" s="1">
         <v>46278</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B257" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C257" s="2" t="s">
@@ -38721,7 +38733,7 @@
       <c r="AA257" s="2" t="s">
         <v>3822</v>
       </c>
-      <c r="AB257" s="9" t="s">
+      <c r="AB257" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38729,7 +38741,7 @@
       <c r="A258" s="1">
         <v>46279</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="B258" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C258" s="2" t="s">
@@ -38807,7 +38819,7 @@
       <c r="AA258" s="2" t="s">
         <v>3836</v>
       </c>
-      <c r="AB258" s="9" t="s">
+      <c r="AB258" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38815,7 +38827,7 @@
       <c r="A259" s="1">
         <v>46280</v>
       </c>
-      <c r="B259" s="2" t="s">
+      <c r="B259" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -38893,7 +38905,7 @@
       <c r="AA259" s="2" t="s">
         <v>3850</v>
       </c>
-      <c r="AB259" s="9" t="s">
+      <c r="AB259" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38901,7 +38913,7 @@
       <c r="A260" s="1">
         <v>46281</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="B260" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C260" s="2" t="s">
@@ -38979,7 +38991,7 @@
       <c r="AA260" s="2" t="s">
         <v>3865</v>
       </c>
-      <c r="AB260" s="9" t="s">
+      <c r="AB260" s="2" t="s">
         <v>3417</v>
       </c>
     </row>
@@ -38987,7 +38999,7 @@
       <c r="A261" s="1">
         <v>46282</v>
       </c>
-      <c r="B261" s="2" t="s">
+      <c r="B261" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C261" s="2" t="s">
@@ -39065,7 +39077,7 @@
       <c r="AA261" s="2" t="s">
         <v>3879</v>
       </c>
-      <c r="AB261" s="9" t="s">
+      <c r="AB261" s="2" t="s">
         <v>3880</v>
       </c>
     </row>
@@ -39073,7 +39085,7 @@
       <c r="A262" s="1">
         <v>46283</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="B262" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C262" s="2" t="s">
@@ -39151,7 +39163,7 @@
       <c r="AA262" s="2" t="s">
         <v>3894</v>
       </c>
-      <c r="AB262" s="9" t="s">
+      <c r="AB262" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39159,7 +39171,7 @@
       <c r="A263" s="1">
         <v>46284</v>
       </c>
-      <c r="B263" s="2" t="s">
+      <c r="B263" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -39237,7 +39249,7 @@
       <c r="AA263" s="2" t="s">
         <v>3908</v>
       </c>
-      <c r="AB263" s="9" t="s">
+      <c r="AB263" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39245,7 +39257,7 @@
       <c r="A264" s="1">
         <v>46285</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="B264" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C264" s="2" t="s">
@@ -39323,7 +39335,7 @@
       <c r="AA264" s="2" t="s">
         <v>3922</v>
       </c>
-      <c r="AB264" s="9" t="s">
+      <c r="AB264" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39331,7 +39343,7 @@
       <c r="A265" s="1">
         <v>46286</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B265" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C265" s="2" t="s">
@@ -39409,7 +39421,7 @@
       <c r="AA265" s="2" t="s">
         <v>3937</v>
       </c>
-      <c r="AB265" s="9" t="s">
+      <c r="AB265" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39417,7 +39429,7 @@
       <c r="A266" s="1">
         <v>46287</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B266" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C266" s="2" t="s">
@@ -39495,7 +39507,7 @@
       <c r="AA266" s="2" t="s">
         <v>3951</v>
       </c>
-      <c r="AB266" s="9" t="s">
+      <c r="AB266" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39503,7 +39515,7 @@
       <c r="A267" s="1">
         <v>46288</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B267" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C267" s="2" t="s">
@@ -39581,7 +39593,7 @@
       <c r="AA267" s="2" t="s">
         <v>3966</v>
       </c>
-      <c r="AB267" s="9" t="s">
+      <c r="AB267" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39589,7 +39601,7 @@
       <c r="A268" s="1">
         <v>46289</v>
       </c>
-      <c r="B268" s="2" t="s">
+      <c r="B268" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C268" s="2" t="s">
@@ -39667,7 +39679,7 @@
       <c r="AA268" s="2" t="s">
         <v>3980</v>
       </c>
-      <c r="AB268" s="9" t="s">
+      <c r="AB268" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -39675,7 +39687,7 @@
       <c r="A269" s="1">
         <v>46290</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B269" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C269" s="2" t="s">
@@ -39753,7 +39765,7 @@
       <c r="AA269" s="2" t="s">
         <v>3994</v>
       </c>
-      <c r="AB269" s="9" t="s">
+      <c r="AB269" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -39761,7 +39773,7 @@
       <c r="A270" s="1">
         <v>46291</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="B270" s="10" t="s">
         <v>3589</v>
       </c>
       <c r="C270" s="2" t="s">
@@ -39839,7 +39851,7 @@
       <c r="AA270" s="2" t="s">
         <v>4009</v>
       </c>
-      <c r="AB270" s="9" t="s">
+      <c r="AB270" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -39847,7 +39859,7 @@
       <c r="A271" s="1">
         <v>46292</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="B271" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C271" s="2" t="s">
@@ -39925,7 +39937,7 @@
       <c r="AA271" s="2" t="s">
         <v>4024</v>
       </c>
-      <c r="AB271" s="9" t="s">
+      <c r="AB271" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -39933,7 +39945,7 @@
       <c r="A272" s="1">
         <v>46293</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="B272" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C272" s="2" t="s">
@@ -40011,7 +40023,7 @@
       <c r="AA272" s="2" t="s">
         <v>4038</v>
       </c>
-      <c r="AB272" s="9" t="s">
+      <c r="AB272" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40019,7 +40031,7 @@
       <c r="A273" s="1">
         <v>46294</v>
       </c>
-      <c r="B273" s="2" t="s">
+      <c r="B273" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C273" s="2" t="s">
@@ -40097,7 +40109,7 @@
       <c r="AA273" s="2" t="s">
         <v>4053</v>
       </c>
-      <c r="AB273" s="9" t="s">
+      <c r="AB273" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40105,7 +40117,7 @@
       <c r="A274" s="1">
         <v>46295</v>
       </c>
-      <c r="B274" s="2" t="s">
+      <c r="B274" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C274" s="2" t="s">
@@ -40183,7 +40195,7 @@
       <c r="AA274" s="2" t="s">
         <v>4069</v>
       </c>
-      <c r="AB274" s="9" t="s">
+      <c r="AB274" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40191,7 +40203,7 @@
       <c r="A275" s="1">
         <v>46296</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="B275" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C275" s="2" t="s">
@@ -40269,7 +40281,7 @@
       <c r="AA275" s="2" t="s">
         <v>4083</v>
       </c>
-      <c r="AB275" s="9" t="s">
+      <c r="AB275" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40277,7 +40289,7 @@
       <c r="A276" s="1">
         <v>46297</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="B276" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C276" s="2" t="s">
@@ -40355,7 +40367,7 @@
       <c r="AA276" s="2" t="s">
         <v>4099</v>
       </c>
-      <c r="AB276" s="9" t="s">
+      <c r="AB276" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40363,7 +40375,7 @@
       <c r="A277" s="1">
         <v>46298</v>
       </c>
-      <c r="B277" s="2" t="s">
+      <c r="B277" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C277" s="2" t="s">
@@ -40441,7 +40453,7 @@
       <c r="AA277" s="2" t="s">
         <v>4113</v>
       </c>
-      <c r="AB277" s="9" t="s">
+      <c r="AB277" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40449,7 +40461,7 @@
       <c r="A278" s="1">
         <v>46299</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="B278" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C278" s="2" t="s">
@@ -40527,7 +40539,7 @@
       <c r="AA278" s="2" t="s">
         <v>4130</v>
       </c>
-      <c r="AB278" s="9" t="s">
+      <c r="AB278" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40535,7 +40547,7 @@
       <c r="A279" s="1">
         <v>46300</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B279" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C279" s="2" t="s">
@@ -40613,7 +40625,7 @@
       <c r="AA279" s="2" t="s">
         <v>4144</v>
       </c>
-      <c r="AB279" s="9" t="s">
+      <c r="AB279" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40621,7 +40633,7 @@
       <c r="A280" s="1">
         <v>46301</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="B280" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C280" s="2" t="s">
@@ -40699,7 +40711,7 @@
       <c r="AA280" s="2" t="s">
         <v>4158</v>
       </c>
-      <c r="AB280" s="9" t="s">
+      <c r="AB280" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40707,7 +40719,7 @@
       <c r="A281" s="1">
         <v>46302</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="B281" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C281" s="2" t="s">
@@ -40785,7 +40797,7 @@
       <c r="AA281" s="2" t="s">
         <v>4173</v>
       </c>
-      <c r="AB281" s="9" t="s">
+      <c r="AB281" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40793,7 +40805,7 @@
       <c r="A282" s="1">
         <v>46303</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="B282" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C282" s="2" t="s">
@@ -40871,7 +40883,7 @@
       <c r="AA282" s="2" t="s">
         <v>4188</v>
       </c>
-      <c r="AB282" s="9" t="s">
+      <c r="AB282" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40879,7 +40891,7 @@
       <c r="A283" s="1">
         <v>46304</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B283" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C283" s="2" t="s">
@@ -40957,7 +40969,7 @@
       <c r="AA283" s="2" t="s">
         <v>4202</v>
       </c>
-      <c r="AB283" s="9" t="s">
+      <c r="AB283" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -40965,7 +40977,7 @@
       <c r="A284" s="1">
         <v>46305</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B284" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C284" s="2" t="s">
@@ -41043,7 +41055,7 @@
       <c r="AA284" s="2" t="s">
         <v>4216</v>
       </c>
-      <c r="AB284" s="9" t="s">
+      <c r="AB284" s="2" t="s">
         <v>3995</v>
       </c>
     </row>
@@ -41051,7 +41063,7 @@
       <c r="A285" s="1">
         <v>46306</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="B285" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C285" s="2" t="s">
@@ -41129,7 +41141,7 @@
       <c r="AA285" s="2" t="s">
         <v>4230</v>
       </c>
-      <c r="AB285" s="9" t="s">
+      <c r="AB285" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41137,7 +41149,7 @@
       <c r="A286" s="1">
         <v>46307</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="B286" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C286" s="2" t="s">
@@ -41215,7 +41227,7 @@
       <c r="AA286" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="AB286" s="9" t="s">
+      <c r="AB286" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41223,7 +41235,7 @@
       <c r="A287" s="1">
         <v>46308</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="B287" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C287" s="2" t="s">
@@ -41301,7 +41313,7 @@
       <c r="AA287" s="2" t="s">
         <v>4260</v>
       </c>
-      <c r="AB287" s="9" t="s">
+      <c r="AB287" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41309,7 +41321,7 @@
       <c r="A288" s="1">
         <v>46309</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="B288" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C288" s="2" t="s">
@@ -41387,7 +41399,7 @@
       <c r="AA288" s="2" t="s">
         <v>4274</v>
       </c>
-      <c r="AB288" s="9" t="s">
+      <c r="AB288" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41395,7 +41407,7 @@
       <c r="A289" s="1">
         <v>46310</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="B289" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C289" s="2" t="s">
@@ -41473,7 +41485,7 @@
       <c r="AA289" s="2" t="s">
         <v>4288</v>
       </c>
-      <c r="AB289" s="9" t="s">
+      <c r="AB289" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41481,7 +41493,7 @@
       <c r="A290" s="1">
         <v>46311</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="B290" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C290" s="2" t="s">
@@ -41559,7 +41571,7 @@
       <c r="AA290" s="2" t="s">
         <v>4302</v>
       </c>
-      <c r="AB290" s="9" t="s">
+      <c r="AB290" s="2" t="s">
         <v>4231</v>
       </c>
     </row>
@@ -41567,7 +41579,7 @@
       <c r="A291" s="1">
         <v>46312</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="B291" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C291" s="2" t="s">
@@ -41645,7 +41657,7 @@
       <c r="AA291" s="2" t="s">
         <v>4316</v>
       </c>
-      <c r="AB291" s="9" t="s">
+      <c r="AB291" s="2" t="s">
         <v>4317</v>
       </c>
     </row>
@@ -41653,7 +41665,7 @@
       <c r="A292" s="1">
         <v>46313</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="B292" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C292" s="2" t="s">
@@ -41731,7 +41743,7 @@
       <c r="AA292" s="2" t="s">
         <v>4332</v>
       </c>
-      <c r="AB292" s="9" t="s">
+      <c r="AB292" s="2" t="s">
         <v>4317</v>
       </c>
     </row>
@@ -41739,7 +41751,7 @@
       <c r="A293" s="1">
         <v>46314</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="B293" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C293" s="2" t="s">
@@ -41817,7 +41829,7 @@
       <c r="AA293" s="2" t="s">
         <v>4345</v>
       </c>
-      <c r="AB293" s="9" t="s">
+      <c r="AB293" s="2" t="s">
         <v>4317</v>
       </c>
     </row>
@@ -41825,7 +41837,7 @@
       <c r="A294" s="1">
         <v>46315</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="B294" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C294" s="2" t="s">
@@ -41903,7 +41915,7 @@
       <c r="AA294" s="2" t="s">
         <v>4360</v>
       </c>
-      <c r="AB294" s="9" t="s">
+      <c r="AB294" s="2" t="s">
         <v>4361</v>
       </c>
     </row>
@@ -41911,7 +41923,7 @@
       <c r="A295" s="1">
         <v>46316</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="B295" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C295" s="2" t="s">
@@ -41989,7 +42001,7 @@
       <c r="AA295" s="2" t="s">
         <v>4375</v>
       </c>
-      <c r="AB295" s="9" t="s">
+      <c r="AB295" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -41997,7 +42009,7 @@
       <c r="A296" s="1">
         <v>46317</v>
       </c>
-      <c r="B296" s="2" t="s">
+      <c r="B296" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C296" s="2" t="s">
@@ -42075,7 +42087,7 @@
       <c r="AA296" s="2" t="s">
         <v>4390</v>
       </c>
-      <c r="AB296" s="9" t="s">
+      <c r="AB296" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42083,7 +42095,7 @@
       <c r="A297" s="1">
         <v>46318</v>
       </c>
-      <c r="B297" s="2" t="s">
+      <c r="B297" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C297" s="2" t="s">
@@ -42161,7 +42173,7 @@
       <c r="AA297" s="2" t="s">
         <v>4405</v>
       </c>
-      <c r="AB297" s="9" t="s">
+      <c r="AB297" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42169,7 +42181,7 @@
       <c r="A298" s="1">
         <v>46319</v>
       </c>
-      <c r="B298" s="2" t="s">
+      <c r="B298" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C298" s="2" t="s">
@@ -42247,7 +42259,7 @@
       <c r="AA298" s="2" t="s">
         <v>4418</v>
       </c>
-      <c r="AB298" s="9" t="s">
+      <c r="AB298" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42255,7 +42267,7 @@
       <c r="A299" s="1">
         <v>46320</v>
       </c>
-      <c r="B299" s="2" t="s">
+      <c r="B299" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C299" s="2" t="s">
@@ -42333,7 +42345,7 @@
       <c r="AA299" s="2" t="s">
         <v>4432</v>
       </c>
-      <c r="AB299" s="9" t="s">
+      <c r="AB299" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42341,7 +42353,7 @@
       <c r="A300" s="1">
         <v>46321</v>
       </c>
-      <c r="B300" s="2" t="s">
+      <c r="B300" s="10" t="s">
         <v>4010</v>
       </c>
       <c r="C300" s="2" t="s">
@@ -42419,7 +42431,7 @@
       <c r="AA300" s="2" t="s">
         <v>4446</v>
       </c>
-      <c r="AB300" s="9" t="s">
+      <c r="AB300" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42427,7 +42439,7 @@
       <c r="A301" s="1">
         <v>46322</v>
       </c>
-      <c r="B301" s="2" t="s">
+      <c r="B301" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C301" s="2" t="s">
@@ -42505,7 +42517,7 @@
       <c r="AA301" s="2" t="s">
         <v>4463</v>
       </c>
-      <c r="AB301" s="9" t="s">
+      <c r="AB301" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42513,7 +42525,7 @@
       <c r="A302" s="1">
         <v>46323</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="B302" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C302" s="2" t="s">
@@ -42591,7 +42603,7 @@
       <c r="AA302" s="2" t="s">
         <v>4477</v>
       </c>
-      <c r="AB302" s="9" t="s">
+      <c r="AB302" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42599,7 +42611,7 @@
       <c r="A303" s="1">
         <v>46324</v>
       </c>
-      <c r="B303" s="2" t="s">
+      <c r="B303" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C303" s="2" t="s">
@@ -42677,7 +42689,7 @@
       <c r="AA303" s="2" t="s">
         <v>4493</v>
       </c>
-      <c r="AB303" s="9" t="s">
+      <c r="AB303" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42685,7 +42697,7 @@
       <c r="A304" s="1">
         <v>46325</v>
       </c>
-      <c r="B304" s="2" t="s">
+      <c r="B304" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C304" s="2" t="s">
@@ -42763,7 +42775,7 @@
       <c r="AA304" s="2" t="s">
         <v>4506</v>
       </c>
-      <c r="AB304" s="9" t="s">
+      <c r="AB304" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42771,7 +42783,7 @@
       <c r="A305" s="1">
         <v>46326</v>
       </c>
-      <c r="B305" s="2" t="s">
+      <c r="B305" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C305" s="2" t="s">
@@ -42849,7 +42861,7 @@
       <c r="AA305" s="2" t="s">
         <v>4521</v>
       </c>
-      <c r="AB305" s="9" t="s">
+      <c r="AB305" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42857,7 +42869,7 @@
       <c r="A306" s="1">
         <v>46327</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="B306" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C306" s="2" t="s">
@@ -42935,7 +42947,7 @@
       <c r="AA306" s="2" t="s">
         <v>4536</v>
       </c>
-      <c r="AB306" s="9" t="s">
+      <c r="AB306" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -42943,7 +42955,7 @@
       <c r="A307" s="1">
         <v>46328</v>
       </c>
-      <c r="B307" s="2" t="s">
+      <c r="B307" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C307" s="2" t="s">
@@ -43021,7 +43033,7 @@
       <c r="AA307" s="2" t="s">
         <v>4550</v>
       </c>
-      <c r="AB307" s="9" t="s">
+      <c r="AB307" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -43029,7 +43041,7 @@
       <c r="A308" s="1">
         <v>46329</v>
       </c>
-      <c r="B308" s="2" t="s">
+      <c r="B308" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C308" s="2" t="s">
@@ -43107,7 +43119,7 @@
       <c r="AA308" s="2" t="s">
         <v>4564</v>
       </c>
-      <c r="AB308" s="9" t="s">
+      <c r="AB308" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -43115,7 +43127,7 @@
       <c r="A309" s="1">
         <v>46330</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="B309" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C309" s="2" t="s">
@@ -43193,7 +43205,7 @@
       <c r="AA309" s="2" t="s">
         <v>4578</v>
       </c>
-      <c r="AB309" s="9" t="s">
+      <c r="AB309" s="2" t="s">
         <v>4376</v>
       </c>
     </row>
@@ -43201,7 +43213,7 @@
       <c r="A310" s="1">
         <v>46331</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="B310" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C310" s="2" t="s">
@@ -43279,7 +43291,7 @@
       <c r="AA310" s="2" t="s">
         <v>4593</v>
       </c>
-      <c r="AB310" s="9" t="s">
+      <c r="AB310" s="2" t="s">
         <v>4594</v>
       </c>
     </row>
@@ -43287,7 +43299,7 @@
       <c r="A311" s="1">
         <v>46332</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="B311" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C311" s="2" t="s">
@@ -43365,7 +43377,7 @@
       <c r="AA311" s="2" t="s">
         <v>4609</v>
       </c>
-      <c r="AB311" s="9" t="s">
+      <c r="AB311" s="2" t="s">
         <v>4610</v>
       </c>
     </row>
@@ -43373,7 +43385,7 @@
       <c r="A312" s="1">
         <v>46333</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="B312" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C312" s="2" t="s">
@@ -43451,7 +43463,7 @@
       <c r="AA312" s="2" t="s">
         <v>4625</v>
       </c>
-      <c r="AB312" s="9" t="s">
+      <c r="AB312" s="2" t="s">
         <v>4610</v>
       </c>
     </row>
@@ -43459,7 +43471,7 @@
       <c r="A313" s="1">
         <v>46334</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="B313" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C313" s="2" t="s">
@@ -43537,7 +43549,7 @@
       <c r="AA313" s="2" t="s">
         <v>4639</v>
       </c>
-      <c r="AB313" s="9" t="s">
+      <c r="AB313" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43545,7 +43557,7 @@
       <c r="A314" s="1">
         <v>46335</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="B314" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C314" s="2" t="s">
@@ -43623,7 +43635,7 @@
       <c r="AA314" s="2" t="s">
         <v>4654</v>
       </c>
-      <c r="AB314" s="9" t="s">
+      <c r="AB314" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43631,7 +43643,7 @@
       <c r="A315" s="1">
         <v>46336</v>
       </c>
-      <c r="B315" s="2" t="s">
+      <c r="B315" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C315" s="2" t="s">
@@ -43709,7 +43721,7 @@
       <c r="AA315" s="2" t="s">
         <v>4668</v>
       </c>
-      <c r="AB315" s="9" t="s">
+      <c r="AB315" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43717,7 +43729,7 @@
       <c r="A316" s="1">
         <v>46337</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B316" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C316" s="2" t="s">
@@ -43795,7 +43807,7 @@
       <c r="AA316" s="2" t="s">
         <v>4682</v>
       </c>
-      <c r="AB316" s="9" t="s">
+      <c r="AB316" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43803,7 +43815,7 @@
       <c r="A317" s="1">
         <v>46338</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="B317" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C317" s="2" t="s">
@@ -43881,7 +43893,7 @@
       <c r="AA317" s="2" t="s">
         <v>4696</v>
       </c>
-      <c r="AB317" s="9" t="s">
+      <c r="AB317" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43889,7 +43901,7 @@
       <c r="A318" s="1">
         <v>46339</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="B318" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C318" s="2" t="s">
@@ -43967,7 +43979,7 @@
       <c r="AA318" s="2" t="s">
         <v>4710</v>
       </c>
-      <c r="AB318" s="9" t="s">
+      <c r="AB318" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -43975,7 +43987,7 @@
       <c r="A319" s="1">
         <v>46340</v>
       </c>
-      <c r="B319" s="2" t="s">
+      <c r="B319" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C319" s="2" t="s">
@@ -44053,7 +44065,7 @@
       <c r="AA319" s="2" t="s">
         <v>4725</v>
       </c>
-      <c r="AB319" s="9" t="s">
+      <c r="AB319" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44061,7 +44073,7 @@
       <c r="A320" s="1">
         <v>46341</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="B320" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C320" s="2" t="s">
@@ -44139,7 +44151,7 @@
       <c r="AA320" s="2" t="s">
         <v>4738</v>
       </c>
-      <c r="AB320" s="9" t="s">
+      <c r="AB320" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44147,7 +44159,7 @@
       <c r="A321" s="1">
         <v>46342</v>
       </c>
-      <c r="B321" s="2" t="s">
+      <c r="B321" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C321" s="2" t="s">
@@ -44225,7 +44237,7 @@
       <c r="AA321" s="2" t="s">
         <v>4752</v>
       </c>
-      <c r="AB321" s="9" t="s">
+      <c r="AB321" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44233,7 +44245,7 @@
       <c r="A322" s="1">
         <v>46343</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="B322" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C322" s="2" t="s">
@@ -44311,7 +44323,7 @@
       <c r="AA322" s="2" t="s">
         <v>4767</v>
       </c>
-      <c r="AB322" s="9" t="s">
+      <c r="AB322" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44319,7 +44331,7 @@
       <c r="A323" s="1">
         <v>46344</v>
       </c>
-      <c r="B323" s="2" t="s">
+      <c r="B323" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C323" s="2" t="s">
@@ -44397,7 +44409,7 @@
       <c r="AA323" s="2" t="s">
         <v>4781</v>
       </c>
-      <c r="AB323" s="9" t="s">
+      <c r="AB323" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44405,7 +44417,7 @@
       <c r="A324" s="1">
         <v>46345</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B324" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C324" s="2" t="s">
@@ -44483,7 +44495,7 @@
       <c r="AA324" s="2" t="s">
         <v>4796</v>
       </c>
-      <c r="AB324" s="9" t="s">
+      <c r="AB324" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44491,7 +44503,7 @@
       <c r="A325" s="1">
         <v>46346</v>
       </c>
-      <c r="B325" s="2" t="s">
+      <c r="B325" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C325" s="2" t="s">
@@ -44569,7 +44581,7 @@
       <c r="AA325" s="2" t="s">
         <v>4810</v>
       </c>
-      <c r="AB325" s="9" t="s">
+      <c r="AB325" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44577,7 +44589,7 @@
       <c r="A326" s="1">
         <v>46347</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="B326" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C326" s="2" t="s">
@@ -44655,7 +44667,7 @@
       <c r="AA326" s="2" t="s">
         <v>4823</v>
       </c>
-      <c r="AB326" s="9" t="s">
+      <c r="AB326" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44663,7 +44675,7 @@
       <c r="A327" s="1">
         <v>46348</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="B327" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C327" s="2" t="s">
@@ -44741,7 +44753,7 @@
       <c r="AA327" s="2" t="s">
         <v>4837</v>
       </c>
-      <c r="AB327" s="9" t="s">
+      <c r="AB327" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44749,7 +44761,7 @@
       <c r="A328" s="1">
         <v>46349</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="B328" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C328" s="2" t="s">
@@ -44827,7 +44839,7 @@
       <c r="AA328" s="2" t="s">
         <v>4851</v>
       </c>
-      <c r="AB328" s="9" t="s">
+      <c r="AB328" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44835,7 +44847,7 @@
       <c r="A329" s="1">
         <v>46350</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="B329" s="10" t="s">
         <v>4447</v>
       </c>
       <c r="C329" s="2" t="s">
@@ -44913,7 +44925,7 @@
       <c r="AA329" s="2" t="s">
         <v>4865</v>
       </c>
-      <c r="AB329" s="9" t="s">
+      <c r="AB329" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -44921,7 +44933,7 @@
       <c r="A330" s="1">
         <v>46351</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="B330" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C330" s="2" t="s">
@@ -44999,7 +45011,7 @@
       <c r="AA330" s="2" t="s">
         <v>4879</v>
       </c>
-      <c r="AB330" s="9" t="s">
+      <c r="AB330" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45007,7 +45019,7 @@
       <c r="A331" s="1">
         <v>46352</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="B331" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C331" s="2" t="s">
@@ -45085,7 +45097,7 @@
       <c r="AA331" s="2" t="s">
         <v>4894</v>
       </c>
-      <c r="AB331" s="9" t="s">
+      <c r="AB331" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45093,7 +45105,7 @@
       <c r="A332" s="1">
         <v>46353</v>
       </c>
-      <c r="B332" s="2" t="s">
+      <c r="B332" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C332" s="2" t="s">
@@ -45171,7 +45183,7 @@
       <c r="AA332" s="2" t="s">
         <v>4909</v>
       </c>
-      <c r="AB332" s="9" t="s">
+      <c r="AB332" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45179,7 +45191,7 @@
       <c r="A333" s="1">
         <v>46354</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="B333" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C333" s="2" t="s">
@@ -45257,7 +45269,7 @@
       <c r="AA333" s="2" t="s">
         <v>4924</v>
       </c>
-      <c r="AB333" s="9" t="s">
+      <c r="AB333" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45265,7 +45277,7 @@
       <c r="A334" s="1">
         <v>46355</v>
       </c>
-      <c r="B334" s="2" t="s">
+      <c r="B334" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C334" s="2" t="s">
@@ -45343,7 +45355,7 @@
       <c r="AA334" s="2" t="s">
         <v>4938</v>
       </c>
-      <c r="AB334" s="9" t="s">
+      <c r="AB334" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45351,7 +45363,7 @@
       <c r="A335" s="1">
         <v>46356</v>
       </c>
-      <c r="B335" s="2" t="s">
+      <c r="B335" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C335" s="2" t="s">
@@ -45429,7 +45441,7 @@
       <c r="AA335" s="2" t="s">
         <v>4954</v>
       </c>
-      <c r="AB335" s="9" t="s">
+      <c r="AB335" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45437,7 +45449,7 @@
       <c r="A336" s="1">
         <v>46357</v>
       </c>
-      <c r="B336" s="2" t="s">
+      <c r="B336" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C336" s="2" t="s">
@@ -45515,7 +45527,7 @@
       <c r="AA336" s="2" t="s">
         <v>4968</v>
       </c>
-      <c r="AB336" s="9" t="s">
+      <c r="AB336" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45523,7 +45535,7 @@
       <c r="A337" s="1">
         <v>46358</v>
       </c>
-      <c r="B337" s="2" t="s">
+      <c r="B337" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C337" s="2" t="s">
@@ -45601,7 +45613,7 @@
       <c r="AA337" s="2" t="s">
         <v>4983</v>
       </c>
-      <c r="AB337" s="9" t="s">
+      <c r="AB337" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45609,7 +45621,7 @@
       <c r="A338" s="1">
         <v>46359</v>
       </c>
-      <c r="B338" s="2" t="s">
+      <c r="B338" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C338" s="2" t="s">
@@ -45687,7 +45699,7 @@
       <c r="AA338" s="2" t="s">
         <v>4996</v>
       </c>
-      <c r="AB338" s="9" t="s">
+      <c r="AB338" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45695,7 +45707,7 @@
       <c r="A339" s="1">
         <v>46360</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="B339" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C339" s="2" t="s">
@@ -45773,7 +45785,7 @@
       <c r="AA339" s="2" t="s">
         <v>5011</v>
       </c>
-      <c r="AB339" s="9" t="s">
+      <c r="AB339" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45781,7 +45793,7 @@
       <c r="A340" s="1">
         <v>46361</v>
       </c>
-      <c r="B340" s="2" t="s">
+      <c r="B340" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C340" s="2" t="s">
@@ -45859,7 +45871,7 @@
       <c r="AA340" s="2" t="s">
         <v>5025</v>
       </c>
-      <c r="AB340" s="9" t="s">
+      <c r="AB340" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45867,7 +45879,7 @@
       <c r="A341" s="1">
         <v>46362</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="B341" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C341" s="2" t="s">
@@ -45945,7 +45957,7 @@
       <c r="AA341" s="2" t="s">
         <v>5039</v>
       </c>
-      <c r="AB341" s="9" t="s">
+      <c r="AB341" s="2" t="s">
         <v>3388</v>
       </c>
     </row>
@@ -45953,7 +45965,7 @@
       <c r="A342" s="1">
         <v>46363</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="B342" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C342" s="2" t="s">
@@ -46031,7 +46043,7 @@
       <c r="AA342" s="2" t="s">
         <v>5054</v>
       </c>
-      <c r="AB342" s="9" t="s">
+      <c r="AB342" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -46039,7 +46051,7 @@
       <c r="A343" s="1">
         <v>46364</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="B343" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C343" s="2" t="s">
@@ -46117,7 +46129,7 @@
       <c r="AA343" s="2" t="s">
         <v>5068</v>
       </c>
-      <c r="AB343" s="9" t="s">
+      <c r="AB343" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -46125,7 +46137,7 @@
       <c r="A344" s="1">
         <v>46365</v>
       </c>
-      <c r="B344" s="2" t="s">
+      <c r="B344" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C344" s="2" t="s">
@@ -46203,7 +46215,7 @@
       <c r="AA344" s="2" t="s">
         <v>5082</v>
       </c>
-      <c r="AB344" s="9" t="s">
+      <c r="AB344" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -46211,7 +46223,7 @@
       <c r="A345" s="1">
         <v>46366</v>
       </c>
-      <c r="B345" s="2" t="s">
+      <c r="B345" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C345" s="2" t="s">
@@ -46289,7 +46301,7 @@
       <c r="AA345" s="2" t="s">
         <v>5096</v>
       </c>
-      <c r="AB345" s="9" t="s">
+      <c r="AB345" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -46297,7 +46309,7 @@
       <c r="A346" s="1">
         <v>46367</v>
       </c>
-      <c r="B346" s="2" t="s">
+      <c r="B346" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C346" s="2" t="s">
@@ -46375,7 +46387,7 @@
       <c r="AA346" s="2" t="s">
         <v>5110</v>
       </c>
-      <c r="AB346" s="9" t="s">
+      <c r="AB346" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -46383,7 +46395,7 @@
       <c r="A347" s="1">
         <v>46368</v>
       </c>
-      <c r="B347" s="2" t="s">
+      <c r="B347" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C347" s="2" t="s">
@@ -46461,7 +46473,7 @@
       <c r="AA347" s="2" t="s">
         <v>5125</v>
       </c>
-      <c r="AB347" s="9" t="s">
+      <c r="AB347" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -46469,7 +46481,7 @@
       <c r="A348" s="1">
         <v>46369</v>
       </c>
-      <c r="B348" s="2" t="s">
+      <c r="B348" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C348" s="2" t="s">
@@ -46547,7 +46559,7 @@
       <c r="AA348" s="2" t="s">
         <v>5138</v>
       </c>
-      <c r="AB348" s="9" t="s">
+      <c r="AB348" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46555,7 +46567,7 @@
       <c r="A349" s="1">
         <v>46370</v>
       </c>
-      <c r="B349" s="2" t="s">
+      <c r="B349" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C349" s="2" t="s">
@@ -46633,7 +46645,7 @@
       <c r="AA349" s="2" t="s">
         <v>5154</v>
       </c>
-      <c r="AB349" s="9" t="s">
+      <c r="AB349" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46641,7 +46653,7 @@
       <c r="A350" s="1">
         <v>46371</v>
       </c>
-      <c r="B350" s="2" t="s">
+      <c r="B350" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C350" s="2" t="s">
@@ -46719,7 +46731,7 @@
       <c r="AA350" s="2" t="s">
         <v>5168</v>
       </c>
-      <c r="AB350" s="9" t="s">
+      <c r="AB350" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46727,7 +46739,7 @@
       <c r="A351" s="1">
         <v>46372</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="B351" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C351" s="2" t="s">
@@ -46805,7 +46817,7 @@
       <c r="AA351" s="2" t="s">
         <v>5183</v>
       </c>
-      <c r="AB351" s="9" t="s">
+      <c r="AB351" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46813,7 +46825,7 @@
       <c r="A352" s="1">
         <v>46373</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="B352" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C352" s="2" t="s">
@@ -46891,7 +46903,7 @@
       <c r="AA352" s="2" t="s">
         <v>5197</v>
       </c>
-      <c r="AB352" s="9" t="s">
+      <c r="AB352" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46899,7 +46911,7 @@
       <c r="A353" s="1">
         <v>46374</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B353" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C353" s="2" t="s">
@@ -46977,7 +46989,7 @@
       <c r="AA353" s="2" t="s">
         <v>5211</v>
       </c>
-      <c r="AB353" s="9" t="s">
+      <c r="AB353" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -46985,7 +46997,7 @@
       <c r="A354" s="1">
         <v>46375</v>
       </c>
-      <c r="B354" s="2" t="s">
+      <c r="B354" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C354" s="2" t="s">
@@ -47063,7 +47075,7 @@
       <c r="AA354" s="2" t="s">
         <v>5226</v>
       </c>
-      <c r="AB354" s="9" t="s">
+      <c r="AB354" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47071,7 +47083,7 @@
       <c r="A355" s="1">
         <v>46376</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="B355" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C355" s="2" t="s">
@@ -47149,7 +47161,7 @@
       <c r="AA355" s="2" t="s">
         <v>5240</v>
       </c>
-      <c r="AB355" s="9" t="s">
+      <c r="AB355" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47157,7 +47169,7 @@
       <c r="A356" s="1">
         <v>46377</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C356" s="2" t="s">
@@ -47235,7 +47247,7 @@
       <c r="AA356" s="2" t="s">
         <v>5255</v>
       </c>
-      <c r="AB356" s="9" t="s">
+      <c r="AB356" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47243,7 +47255,7 @@
       <c r="A357" s="1">
         <v>46378</v>
       </c>
-      <c r="B357" s="2" t="s">
+      <c r="B357" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C357" s="2" t="s">
@@ -47321,7 +47333,7 @@
       <c r="AA357" s="2" t="s">
         <v>5268</v>
       </c>
-      <c r="AB357" s="9" t="s">
+      <c r="AB357" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47329,7 +47341,7 @@
       <c r="A358" s="1">
         <v>46379</v>
       </c>
-      <c r="B358" s="2" t="s">
+      <c r="B358" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C358" s="2" t="s">
@@ -47407,7 +47419,7 @@
       <c r="AA358" s="2" t="s">
         <v>5283</v>
       </c>
-      <c r="AB358" s="9" t="s">
+      <c r="AB358" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47415,7 +47427,7 @@
       <c r="A359" s="1">
         <v>46380</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="B359" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C359" s="2" t="s">
@@ -47493,7 +47505,7 @@
       <c r="AA359" s="2" t="s">
         <v>5298</v>
       </c>
-      <c r="AB359" s="9" t="s">
+      <c r="AB359" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47501,7 +47513,7 @@
       <c r="A360" s="1">
         <v>46381</v>
       </c>
-      <c r="B360" s="2" t="s">
+      <c r="B360" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C360" s="2" t="s">
@@ -47579,7 +47591,7 @@
       <c r="AA360" s="2" t="s">
         <v>5312</v>
       </c>
-      <c r="AB360" s="9" t="s">
+      <c r="AB360" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47587,7 +47599,7 @@
       <c r="A361" s="1">
         <v>46382</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B361" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C361" s="2" t="s">
@@ -47665,7 +47677,7 @@
       <c r="AA361" s="2" t="s">
         <v>5327</v>
       </c>
-      <c r="AB361" s="9" t="s">
+      <c r="AB361" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47673,7 +47685,7 @@
       <c r="A362" s="1">
         <v>46383</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B362" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C362" s="2" t="s">
@@ -47751,7 +47763,7 @@
       <c r="AA362" s="2" t="s">
         <v>5341</v>
       </c>
-      <c r="AB362" s="9" t="s">
+      <c r="AB362" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47759,7 +47771,7 @@
       <c r="A363" s="1">
         <v>46384</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="B363" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C363" s="2" t="s">
@@ -47837,7 +47849,7 @@
       <c r="AA363" s="2" t="s">
         <v>5355</v>
       </c>
-      <c r="AB363" s="9" t="s">
+      <c r="AB363" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47845,7 +47857,7 @@
       <c r="A364" s="1">
         <v>46385</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="B364" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C364" s="2" t="s">
@@ -47923,7 +47935,7 @@
       <c r="AA364" s="2" t="s">
         <v>5371</v>
       </c>
-      <c r="AB364" s="9" t="s">
+      <c r="AB364" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -47931,7 +47943,7 @@
       <c r="A365" s="1">
         <v>46386</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="B365" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C365" s="2" t="s">
@@ -48009,7 +48021,7 @@
       <c r="AA365" s="2" t="s">
         <v>5385</v>
       </c>
-      <c r="AB365" s="9" t="s">
+      <c r="AB365" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
@@ -48017,7 +48029,7 @@
       <c r="A366" s="1">
         <v>46387</v>
       </c>
-      <c r="B366" s="2" t="s">
+      <c r="B366" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C366" s="2" t="s">
@@ -48095,7 +48107,7 @@
       <c r="AA366" s="2" t="s">
         <v>5398</v>
       </c>
-      <c r="AB366" s="9" t="s">
+      <c r="AB366" s="2" t="s">
         <v>5139</v>
       </c>
     </row>
